--- a/data/SPO_review_level.xlsx
+++ b/data/SPO_review_level.xlsx
@@ -62,7 +62,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetData>
-    <row r="1" spans="1:177">
+    <row r="1" spans="1:182">
       <c r="A1" s="0" t="inlineStr">
         <is>
           <t>Refid</t>
@@ -105,857 +105,882 @@
       </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
+          <t>review_funding_source</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
           <t>review_publication_year</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <is>
           <t>review_databases_searched</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>review_search_date</t>
         </is>
       </c>
-      <c r="L1" s="0" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>review_number_studies</t>
         </is>
       </c>
-      <c r="M1" s="0" t="inlineStr">
+      <c r="N1" s="0" t="inlineStr">
         <is>
           <t>review_flow_diagram</t>
         </is>
       </c>
-      <c r="N1" s="0" t="inlineStr">
+      <c r="O1" s="0" t="inlineStr">
         <is>
           <t>review_registration_number</t>
         </is>
       </c>
-      <c r="O1" s="0" t="inlineStr">
+      <c r="P1" s="0" t="inlineStr">
         <is>
           <t>review_availability_statement</t>
         </is>
       </c>
-      <c r="P1" s="0" t="inlineStr">
+      <c r="Q1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_participant</t>
         </is>
       </c>
-      <c r="Q1" s="0" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_intervention</t>
         </is>
       </c>
-      <c r="R1" s="0" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_comparator</t>
         </is>
       </c>
-      <c r="S1" s="0" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_outcome</t>
         </is>
       </c>
-      <c r="T1" s="0" t="inlineStr">
+      <c r="U1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_timing</t>
         </is>
       </c>
-      <c r="U1" s="0" t="inlineStr">
+      <c r="V1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_setting</t>
         </is>
       </c>
-      <c r="V1" s="0" t="inlineStr">
+      <c r="W1" s="0" t="inlineStr">
         <is>
           <t>review_eligibility_design</t>
         </is>
       </c>
-      <c r="W1" s="0" t="inlineStr">
+      <c r="X1" s="0" t="inlineStr">
         <is>
           <t>review_main_focus -&gt; Suicide</t>
         </is>
       </c>
-      <c r="X1" s="0" t="inlineStr">
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>review_main_focus -&gt; Prevention</t>
         </is>
       </c>
-      <c r="Y1" s="0" t="inlineStr">
+      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>review_main_focus -&gt; School-aged youth</t>
         </is>
       </c>
-      <c r="Z1" s="0" t="inlineStr">
+      <c r="AA1" s="0" t="inlineStr">
         <is>
           <t>review_main_focus -&gt; School settings</t>
         </is>
       </c>
-      <c r="AA1" s="0" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
+        <is>
+          <t>review_rob_flag</t>
+        </is>
+      </c>
+      <c r="AC1" s="0" t="inlineStr">
+        <is>
+          <t>review_rob_tool</t>
+        </is>
+      </c>
+      <c r="AD1" s="0" t="inlineStr">
+        <is>
+          <t>review_rob_exclude</t>
+        </is>
+      </c>
+      <c r="AE1" s="0" t="inlineStr">
+        <is>
+          <t>review_rob_concern</t>
+        </is>
+      </c>
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_pico -&gt; Population</t>
         </is>
       </c>
-      <c r="AB1" s="0" t="inlineStr">
+      <c r="AG1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_pico -&gt; Intervention</t>
         </is>
       </c>
-      <c r="AC1" s="0" t="inlineStr">
+      <c r="AH1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_pico -&gt; Comparator group</t>
         </is>
       </c>
-      <c r="AD1" s="0" t="inlineStr">
+      <c r="AI1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_pico -&gt; Outcome</t>
         </is>
       </c>
-      <c r="AE1" s="0" t="inlineStr">
+      <c r="AJ1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_explanation</t>
         </is>
       </c>
-      <c r="AF1" s="0" t="inlineStr">
+      <c r="AK1" s="0" t="inlineStr">
         <is>
           <t>amstar_1_rating</t>
         </is>
       </c>
-      <c r="AG1" s="0" t="inlineStr">
+      <c r="AL1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_partialyes -&gt; review questions</t>
         </is>
       </c>
-      <c r="AH1" s="0" t="inlineStr">
+      <c r="AM1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_partialyes -&gt; a search strategy</t>
         </is>
       </c>
-      <c r="AI1" s="0" t="inlineStr">
+      <c r="AN1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_partialyes -&gt; inclusion/exclusion criteria</t>
         </is>
       </c>
-      <c r="AJ1" s="0" t="inlineStr">
+      <c r="AO1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_partialyes -&gt; a risk of bias assessment</t>
         </is>
       </c>
-      <c r="AK1" s="0" t="inlineStr">
+      <c r="AP1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_yes -&gt; a meta-analysis/synthesis plan, if appropriate (in the protocol), and</t>
         </is>
       </c>
-      <c r="AL1" s="0" t="inlineStr">
+      <c r="AQ1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_yes -&gt; a plan for investigating causes of heterogeneity (in the protocol)</t>
         </is>
       </c>
-      <c r="AM1" s="0" t="inlineStr">
+      <c r="AR1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_yes -&gt; justification for any deviations from the protocol (typically reported in the manuscript)</t>
         </is>
       </c>
-      <c r="AN1" s="0" t="inlineStr">
+      <c r="AS1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_explanation</t>
         </is>
       </c>
-      <c r="AO1" s="0" t="inlineStr">
+      <c r="AT1" s="0" t="inlineStr">
         <is>
           <t>amstar_2_rating</t>
         </is>
       </c>
-      <c r="AP1" s="0" t="inlineStr">
+      <c r="AU1" s="0" t="inlineStr">
         <is>
           <t>amstar_3_design -&gt; Explanation for including only RCTs</t>
         </is>
       </c>
-      <c r="AQ1" s="0" t="inlineStr">
+      <c r="AV1" s="0" t="inlineStr">
         <is>
           <t>amstar_3_design -&gt; OR Explanation for including both RCTs and NRSI</t>
         </is>
       </c>
-      <c r="AR1" s="0" t="inlineStr">
+      <c r="AW1" s="0" t="inlineStr">
         <is>
           <t>amstar_3_explanation</t>
         </is>
       </c>
-      <c r="AS1" s="0" t="inlineStr">
+      <c r="AX1" s="0" t="inlineStr">
         <is>
           <t>amstar_3_rating</t>
         </is>
       </c>
-      <c r="AT1" s="0" t="inlineStr">
+      <c r="AY1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_partialyes -&gt; searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU1" s="0" t="inlineStr">
+      <c r="AZ1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_partialyes -&gt; provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AV1" s="0" t="inlineStr">
+      <c r="BA1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_partialyes -&gt; justified publication restrictions (e.g. language)</t>
         </is>
       </c>
-      <c r="AW1" s="0" t="inlineStr">
+      <c r="BB1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_yes -&gt; searched the reference lists/bibliographies of included studies</t>
         </is>
       </c>
-      <c r="AX1" s="0" t="inlineStr">
+      <c r="BC1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_yes -&gt; searched trial/study registries</t>
         </is>
       </c>
-      <c r="AY1" s="0" t="inlineStr">
+      <c r="BD1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_yes -&gt; where relevant, searched for grey literature</t>
         </is>
       </c>
-      <c r="AZ1" s="0" t="inlineStr">
+      <c r="BE1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_yes -&gt; conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA1" s="0" t="inlineStr">
+      <c r="BF1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_explanation</t>
         </is>
       </c>
-      <c r="BB1" s="0" t="inlineStr">
+      <c r="BG1" s="0" t="inlineStr">
         <is>
           <t>amstar_4_rating</t>
         </is>
       </c>
-      <c r="BC1" s="0" t="inlineStr">
+      <c r="BH1" s="0" t="inlineStr">
         <is>
           <t>amstar_5_selection -&gt; at least two reviewers independently agreed on selection of eligible studies and achieved consensus on which studies to include</t>
         </is>
       </c>
-      <c r="BD1" s="0" t="inlineStr">
+      <c r="BI1" s="0" t="inlineStr">
         <is>
           <t>amstar_5_selection -&gt; OR two reviewers selected a sample of eligible studies and achieved good agreement (at least 80 percent), with the remainder selected by one reviewer</t>
         </is>
       </c>
-      <c r="BE1" s="0" t="inlineStr">
+      <c r="BJ1" s="0" t="inlineStr">
         <is>
           <t>amstar_5_explanation</t>
         </is>
       </c>
-      <c r="BF1" s="0" t="inlineStr">
+      <c r="BK1" s="0" t="inlineStr">
         <is>
           <t>amstar_5_rating</t>
         </is>
       </c>
-      <c r="BG1" s="0" t="inlineStr">
+      <c r="BL1" s="0" t="inlineStr">
         <is>
           <t>amstar_6_extraction -&gt; at least two reviewers achieved consensus on which data to extract from included studies</t>
         </is>
       </c>
-      <c r="BH1" s="0" t="inlineStr">
+      <c r="BM1" s="0" t="inlineStr">
         <is>
           <t>amstar_6_explanation</t>
         </is>
       </c>
-      <c r="BI1" s="0" t="inlineStr">
+      <c r="BN1" s="0" t="inlineStr">
         <is>
           <t>amstar_6_rating</t>
         </is>
       </c>
-      <c r="BJ1" s="0" t="inlineStr">
+      <c r="BO1" s="0" t="inlineStr">
         <is>
           <t>amstar_7_explanation</t>
         </is>
       </c>
-      <c r="BK1" s="0" t="inlineStr">
+      <c r="BP1" s="0" t="inlineStr">
         <is>
           <t>amstar_7_rating</t>
         </is>
       </c>
-      <c r="BL1" s="0" t="inlineStr">
+      <c r="BQ1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_partialyes -&gt; described populations</t>
         </is>
       </c>
-      <c r="BM1" s="0" t="inlineStr">
+      <c r="BR1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_partialyes -&gt; described interventions</t>
         </is>
       </c>
-      <c r="BN1" s="0" t="inlineStr">
+      <c r="BS1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_partialyes -&gt; described comparators</t>
         </is>
       </c>
-      <c r="BO1" s="0" t="inlineStr">
+      <c r="BT1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_partialyes -&gt; described outcomes</t>
         </is>
       </c>
-      <c r="BP1" s="0" t="inlineStr">
+      <c r="BU1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_partialyes -&gt; described research designs</t>
         </is>
       </c>
-      <c r="BQ1" s="0" t="inlineStr">
+      <c r="BV1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_yes -&gt; described population in detail</t>
         </is>
       </c>
-      <c r="BR1" s="0" t="inlineStr">
+      <c r="BW1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_yes -&gt; described intervention and comparator in detail (including doses where relevant)</t>
         </is>
       </c>
-      <c r="BS1" s="0" t="inlineStr">
+      <c r="BX1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_yes -&gt; described study's setting</t>
         </is>
       </c>
-      <c r="BT1" s="0" t="inlineStr">
+      <c r="BY1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_yes -&gt; timeframe for follow-up</t>
         </is>
       </c>
-      <c r="BU1" s="0" t="inlineStr">
+      <c r="BZ1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_explanation</t>
         </is>
       </c>
-      <c r="BV1" s="0" t="inlineStr">
+      <c r="CA1" s="0" t="inlineStr">
         <is>
           <t>amstar_8_rating</t>
         </is>
       </c>
-      <c r="BW1" s="0" t="inlineStr">
+      <c r="CB1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_partialyes -&gt; unconcealed allocation, and</t>
         </is>
       </c>
-      <c r="BX1" s="0" t="inlineStr">
+      <c r="CC1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_partialyes -&gt; lack of blinding of patients and assessors when assessing outcomes (unnecessary for objective outcomes such as all cause mortality)</t>
         </is>
       </c>
-      <c r="BY1" s="0" t="inlineStr">
+      <c r="CD1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_yes -&gt; allocation sequence that was not truly random, and</t>
         </is>
       </c>
-      <c r="BZ1" s="0" t="inlineStr">
+      <c r="CE1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_yes -&gt; selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CA1" s="0" t="inlineStr">
+      <c r="CF1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_explanation</t>
         </is>
       </c>
-      <c r="CB1" s="0" t="inlineStr">
+      <c r="CG1" s="0" t="inlineStr">
         <is>
           <t>amstar_9rct_rating</t>
         </is>
       </c>
-      <c r="CC1" s="0" t="inlineStr">
+      <c r="CH1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_partialyes -&gt; confounding, and</t>
         </is>
       </c>
-      <c r="CD1" s="0" t="inlineStr">
+      <c r="CI1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_partialyes -&gt; selection bias</t>
         </is>
       </c>
-      <c r="CE1" s="0" t="inlineStr">
+      <c r="CJ1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_yes -&gt; methods used to ascertain exposures and outcomes, and</t>
         </is>
       </c>
-      <c r="CF1" s="0" t="inlineStr">
+      <c r="CK1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_yes -&gt; selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CG1" s="0" t="inlineStr">
+      <c r="CL1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_onlynrsi -&gt; Includes only RCT</t>
         </is>
       </c>
-      <c r="CH1" s="0" t="inlineStr">
+      <c r="CM1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_explanation</t>
         </is>
       </c>
-      <c r="CI1" s="0" t="inlineStr">
+      <c r="CN1" s="0" t="inlineStr">
         <is>
           <t>amstar_9nrsi_rating</t>
         </is>
       </c>
-      <c r="CJ1" s="0" t="inlineStr">
+      <c r="CO1" s="0" t="inlineStr">
         <is>
           <t>amstar_10_explanation</t>
         </is>
       </c>
-      <c r="CK1" s="0" t="inlineStr">
+      <c r="CP1" s="0" t="inlineStr">
         <is>
           <t>amstar_10_rating</t>
         </is>
       </c>
-      <c r="CL1" s="0" t="inlineStr">
+      <c r="CQ1" s="0" t="inlineStr">
         <is>
           <t>amstar_11rct_results -&gt; The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM1" s="0" t="inlineStr">
+      <c r="CR1" s="0" t="inlineStr">
         <is>
           <t>amstar_11rct_results -&gt; AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN1" s="0" t="inlineStr">
+      <c r="CS1" s="0" t="inlineStr">
         <is>
           <t>amstar_11rct_results -&gt; AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO1" s="0" t="inlineStr">
+      <c r="CT1" s="0" t="inlineStr">
         <is>
           <t>amstar_11rct_explanation</t>
         </is>
       </c>
-      <c r="CP1" s="0" t="inlineStr">
+      <c r="CU1" s="0" t="inlineStr">
         <is>
           <t>amstar_11rct_rating</t>
         </is>
       </c>
-      <c r="CQ1" s="0" t="inlineStr">
+      <c r="CV1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_results -&gt; The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CR1" s="0" t="inlineStr">
+      <c r="CW1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_results -&gt; AND they used an appropriate weighted technique to combine study results, adjusting for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CS1" s="0" t="inlineStr">
+      <c r="CX1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_results -&gt; AND they statistically combined effect estimates from NRSI that were adjusted for confounding, rather than combining raw data, or justified combining raw data when adjusted effect estimates were not available</t>
         </is>
       </c>
-      <c r="CT1" s="0" t="inlineStr">
+      <c r="CY1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_nometa -&gt; No NRSIs</t>
         </is>
       </c>
-      <c r="CU1" s="0" t="inlineStr">
+      <c r="CZ1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_explanation</t>
         </is>
       </c>
-      <c r="CV1" s="0" t="inlineStr">
+      <c r="DA1" s="0" t="inlineStr">
         <is>
           <t>amstar_11nrsi_rating</t>
         </is>
       </c>
-      <c r="CW1" s="0" t="inlineStr">
+      <c r="DB1" s="0" t="inlineStr">
         <is>
           <t>amstar_12_robmeta -&gt; OR, if the pooled estimate was based on RCTs and/or NRSI at variable RoB, the authors performed analyses to investigate possible impact of RoB on summary estimates of effect</t>
         </is>
       </c>
-      <c r="CX1" s="0" t="inlineStr">
+      <c r="DC1" s="0" t="inlineStr">
         <is>
           <t>amstar_12_explanation</t>
         </is>
       </c>
-      <c r="CY1" s="0" t="inlineStr">
+      <c r="DD1" s="0" t="inlineStr">
         <is>
           <t>amstar_12_rating</t>
         </is>
       </c>
-      <c r="CZ1" s="0" t="inlineStr">
+      <c r="DE1" s="0" t="inlineStr">
         <is>
           <t>amstar_13_robstudies -&gt; OR, if RCTs with moderate or high RoB, or NRSI were included the review provided a discussion of the likely impact of RoB on the results</t>
         </is>
       </c>
-      <c r="DA1" s="0" t="inlineStr">
+      <c r="DF1" s="0" t="inlineStr">
         <is>
           <t>amstar_13_explanation</t>
         </is>
       </c>
-      <c r="DB1" s="0" t="inlineStr">
+      <c r="DG1" s="0" t="inlineStr">
         <is>
           <t>amstar_13_rating</t>
         </is>
       </c>
-      <c r="DC1" s="0" t="inlineStr">
+      <c r="DH1" s="0" t="inlineStr">
         <is>
           <t>amstar_14_heterogeneity -&gt; There was no significant heterogeneity in the results</t>
         </is>
       </c>
-      <c r="DD1" s="0" t="inlineStr">
+      <c r="DI1" s="0" t="inlineStr">
         <is>
           <t>amstar_14_heterogeneity -&gt; OR if heterogeneity was present the authors performed an investigation of sources of any heterogeneity in the results and discussed the impact of this on the results of the review</t>
         </is>
       </c>
-      <c r="DE1" s="0" t="inlineStr">
+      <c r="DJ1" s="0" t="inlineStr">
         <is>
           <t>amstar_14_explanation</t>
         </is>
       </c>
-      <c r="DF1" s="0" t="inlineStr">
+      <c r="DK1" s="0" t="inlineStr">
         <is>
           <t>amstar_14_rating</t>
         </is>
       </c>
-      <c r="DG1" s="0" t="inlineStr">
+      <c r="DL1" s="0" t="inlineStr">
         <is>
           <t>amstar_15_pubbias -&gt; performed graphical or statistical tests for publication bias and discussed the likelihood and magnitude of impact of publication bias</t>
         </is>
       </c>
-      <c r="DH1" s="0" t="inlineStr">
+      <c r="DM1" s="0" t="inlineStr">
         <is>
           <t>amstar_15_explanation</t>
         </is>
       </c>
-      <c r="DI1" s="0" t="inlineStr">
+      <c r="DN1" s="0" t="inlineStr">
         <is>
           <t>amstar_15_rating</t>
         </is>
       </c>
-      <c r="DJ1" s="0" t="inlineStr">
+      <c r="DO1" s="0" t="inlineStr">
         <is>
           <t>amstar_16_coi -&gt; The authors reported no competing interests OR</t>
         </is>
       </c>
-      <c r="DK1" s="0" t="inlineStr">
+      <c r="DP1" s="0" t="inlineStr">
         <is>
           <t>amstar_16_coi -&gt; The authors described their funding sources and how they managed potential conflicts of interest</t>
         </is>
       </c>
-      <c r="DL1" s="0" t="inlineStr">
+      <c r="DQ1" s="0" t="inlineStr">
         <is>
           <t>amstar_16_explanation</t>
         </is>
       </c>
-      <c r="DM1" s="0" t="inlineStr">
+      <c r="DR1" s="0" t="inlineStr">
         <is>
           <t>amstar_16_rating</t>
         </is>
       </c>
-      <c r="DN1" s="0" t="inlineStr">
+      <c r="DS1" s="0" t="inlineStr">
         <is>
           <t>amstar_overall_rating</t>
         </is>
       </c>
-      <c r="DO1" s="0" t="inlineStr">
+      <c r="DT1" s="0" t="inlineStr">
         <is>
           <t>amstar_overall_explanation</t>
         </is>
       </c>
-      <c r="DP1" s="0" t="inlineStr">
+      <c r="DU1" s="0" t="inlineStr">
         <is>
           <t>robis_1.1_rating</t>
         </is>
       </c>
-      <c r="DQ1" s="0" t="inlineStr">
+      <c r="DV1" s="0" t="inlineStr">
         <is>
           <t>robis_1.1_explanation</t>
         </is>
       </c>
-      <c r="DR1" s="0" t="inlineStr">
+      <c r="DW1" s="0" t="inlineStr">
         <is>
           <t>robis_1.2_rating</t>
         </is>
       </c>
-      <c r="DS1" s="0" t="inlineStr">
+      <c r="DX1" s="0" t="inlineStr">
         <is>
           <t>robis_1.2_explanation</t>
         </is>
       </c>
-      <c r="DT1" s="0" t="inlineStr">
+      <c r="DY1" s="0" t="inlineStr">
         <is>
           <t>robis_1.3_rating</t>
         </is>
       </c>
-      <c r="DU1" s="0" t="inlineStr">
+      <c r="DZ1" s="0" t="inlineStr">
         <is>
           <t>robis_1.3_explanation</t>
         </is>
       </c>
-      <c r="DV1" s="0" t="inlineStr">
+      <c r="EA1" s="0" t="inlineStr">
         <is>
           <t>robis_1.4_rating</t>
         </is>
       </c>
-      <c r="DW1" s="0" t="inlineStr">
+      <c r="EB1" s="0" t="inlineStr">
         <is>
           <t>robis_1.4_explanation</t>
         </is>
       </c>
-      <c r="DX1" s="0" t="inlineStr">
+      <c r="EC1" s="0" t="inlineStr">
         <is>
           <t>robis_1.5_rating</t>
         </is>
       </c>
-      <c r="DY1" s="0" t="inlineStr">
+      <c r="ED1" s="0" t="inlineStr">
         <is>
           <t>robis_1.5_explanation</t>
         </is>
       </c>
-      <c r="DZ1" s="0" t="inlineStr">
+      <c r="EE1" s="0" t="inlineStr">
         <is>
           <t>robis_1_decision</t>
         </is>
       </c>
-      <c r="EA1" s="0" t="inlineStr">
+      <c r="EF1" s="0" t="inlineStr">
         <is>
           <t>robis_1_explanation</t>
         </is>
       </c>
-      <c r="EB1" s="0" t="inlineStr">
+      <c r="EG1" s="0" t="inlineStr">
         <is>
           <t>robis_2.1_rating</t>
         </is>
       </c>
-      <c r="EC1" s="0" t="inlineStr">
+      <c r="EH1" s="0" t="inlineStr">
         <is>
           <t>robis_2.1_explanation</t>
         </is>
       </c>
-      <c r="ED1" s="0" t="inlineStr">
+      <c r="EI1" s="0" t="inlineStr">
         <is>
           <t>robis_2.2_rating</t>
         </is>
       </c>
-      <c r="EE1" s="0" t="inlineStr">
+      <c r="EJ1" s="0" t="inlineStr">
         <is>
           <t>robis_2.2_explanation</t>
         </is>
       </c>
-      <c r="EF1" s="0" t="inlineStr">
+      <c r="EK1" s="0" t="inlineStr">
         <is>
           <t>robis_2.3_rating</t>
         </is>
       </c>
-      <c r="EG1" s="0" t="inlineStr">
+      <c r="EL1" s="0" t="inlineStr">
         <is>
           <t>robis_2.3_explanation</t>
         </is>
       </c>
-      <c r="EH1" s="0" t="inlineStr">
+      <c r="EM1" s="0" t="inlineStr">
         <is>
           <t>robis_2.4_rating</t>
         </is>
       </c>
-      <c r="EI1" s="0" t="inlineStr">
+      <c r="EN1" s="0" t="inlineStr">
         <is>
           <t>robis_2.4_explanation</t>
         </is>
       </c>
-      <c r="EJ1" s="0" t="inlineStr">
+      <c r="EO1" s="0" t="inlineStr">
         <is>
           <t>robis_2.5_rating</t>
         </is>
       </c>
-      <c r="EK1" s="0" t="inlineStr">
+      <c r="EP1" s="0" t="inlineStr">
         <is>
           <t>robis_2.5_explanation</t>
         </is>
       </c>
-      <c r="EL1" s="0" t="inlineStr">
+      <c r="EQ1" s="0" t="inlineStr">
         <is>
           <t>robis_2_decision</t>
         </is>
       </c>
-      <c r="EM1" s="0" t="inlineStr">
+      <c r="ER1" s="0" t="inlineStr">
         <is>
           <t>robis_2_explanation</t>
         </is>
       </c>
-      <c r="EN1" s="0" t="inlineStr">
+      <c r="ES1" s="0" t="inlineStr">
         <is>
           <t>robis_3.1_rating</t>
         </is>
       </c>
-      <c r="EO1" s="0" t="inlineStr">
+      <c r="ET1" s="0" t="inlineStr">
         <is>
           <t>robis_3.1_explanation</t>
         </is>
       </c>
-      <c r="EP1" s="0" t="inlineStr">
+      <c r="EU1" s="0" t="inlineStr">
         <is>
           <t>robis_3.2_rating</t>
         </is>
       </c>
-      <c r="EQ1" s="0" t="inlineStr">
+      <c r="EV1" s="0" t="inlineStr">
         <is>
           <t>robis_3.2_explanation</t>
         </is>
       </c>
-      <c r="ER1" s="0" t="inlineStr">
+      <c r="EW1" s="0" t="inlineStr">
         <is>
           <t>robis_3.3_rating</t>
         </is>
       </c>
-      <c r="ES1" s="0" t="inlineStr">
+      <c r="EX1" s="0" t="inlineStr">
         <is>
           <t>robis_3.3_explanation</t>
         </is>
       </c>
-      <c r="ET1" s="0" t="inlineStr">
+      <c r="EY1" s="0" t="inlineStr">
         <is>
           <t>robis_3.4_rating</t>
         </is>
       </c>
-      <c r="EU1" s="0" t="inlineStr">
+      <c r="EZ1" s="0" t="inlineStr">
         <is>
           <t>robis_3.4_explanation</t>
         </is>
       </c>
-      <c r="EV1" s="0" t="inlineStr">
+      <c r="FA1" s="0" t="inlineStr">
         <is>
           <t>robis_3.5_rating</t>
         </is>
       </c>
-      <c r="EW1" s="0" t="inlineStr">
+      <c r="FB1" s="0" t="inlineStr">
         <is>
           <t>robis_3.5_explanation</t>
         </is>
       </c>
-      <c r="EX1" s="0" t="inlineStr">
+      <c r="FC1" s="0" t="inlineStr">
         <is>
           <t>robis_3_decision</t>
         </is>
       </c>
-      <c r="EY1" s="0" t="inlineStr">
+      <c r="FD1" s="0" t="inlineStr">
         <is>
           <t>robis_3_explanation</t>
         </is>
       </c>
-      <c r="EZ1" s="0" t="inlineStr">
+      <c r="FE1" s="0" t="inlineStr">
         <is>
           <t>robis_4.1_rating</t>
         </is>
       </c>
-      <c r="FA1" s="0" t="inlineStr">
+      <c r="FF1" s="0" t="inlineStr">
         <is>
           <t>robis_4.1_explanation</t>
         </is>
       </c>
-      <c r="FB1" s="0" t="inlineStr">
+      <c r="FG1" s="0" t="inlineStr">
         <is>
           <t>robis_4.2_rating</t>
         </is>
       </c>
-      <c r="FC1" s="0" t="inlineStr">
+      <c r="FH1" s="0" t="inlineStr">
         <is>
           <t>robis_4.2_explanation</t>
         </is>
       </c>
-      <c r="FD1" s="0" t="inlineStr">
+      <c r="FI1" s="0" t="inlineStr">
         <is>
           <t>robis_4.3_rating</t>
         </is>
       </c>
-      <c r="FE1" s="0" t="inlineStr">
+      <c r="FJ1" s="0" t="inlineStr">
         <is>
           <t>robis_4.3_explanation</t>
         </is>
       </c>
-      <c r="FF1" s="0" t="inlineStr">
+      <c r="FK1" s="0" t="inlineStr">
         <is>
           <t>robis_4.4_rating</t>
         </is>
       </c>
-      <c r="FG1" s="0" t="inlineStr">
+      <c r="FL1" s="0" t="inlineStr">
         <is>
           <t>robis_4.4_explanation</t>
         </is>
       </c>
-      <c r="FH1" s="0" t="inlineStr">
+      <c r="FM1" s="0" t="inlineStr">
         <is>
           <t>robis_4.5_rating</t>
         </is>
       </c>
-      <c r="FI1" s="0" t="inlineStr">
+      <c r="FN1" s="0" t="inlineStr">
         <is>
           <t>robis_4.5_explanation</t>
         </is>
       </c>
-      <c r="FJ1" s="0" t="inlineStr">
+      <c r="FO1" s="0" t="inlineStr">
         <is>
           <t>robis_4.6_rating</t>
         </is>
       </c>
-      <c r="FK1" s="0" t="inlineStr">
+      <c r="FP1" s="0" t="inlineStr">
         <is>
           <t>robis_4.6_explanation</t>
         </is>
       </c>
-      <c r="FL1" s="0" t="inlineStr">
+      <c r="FQ1" s="0" t="inlineStr">
         <is>
           <t>robis_4_decision</t>
         </is>
       </c>
-      <c r="FM1" s="0" t="inlineStr">
+      <c r="FR1" s="0" t="inlineStr">
         <is>
           <t>robis_4_explanation</t>
         </is>
       </c>
-      <c r="FN1" s="0" t="inlineStr">
+      <c r="FS1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_a</t>
         </is>
       </c>
-      <c r="FO1" s="0" t="inlineStr">
+      <c r="FT1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_a_explanation</t>
         </is>
       </c>
-      <c r="FP1" s="0" t="inlineStr">
+      <c r="FU1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_b</t>
         </is>
       </c>
-      <c r="FQ1" s="0" t="inlineStr">
+      <c r="FV1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_b_explanation</t>
         </is>
       </c>
-      <c r="FR1" s="0" t="inlineStr">
+      <c r="FW1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_c</t>
         </is>
       </c>
-      <c r="FS1" s="0" t="inlineStr">
+      <c r="FX1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_c_explanation</t>
         </is>
       </c>
-      <c r="FT1" s="0" t="inlineStr">
+      <c r="FY1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_rating</t>
         </is>
       </c>
-      <c r="FU1" s="0" t="inlineStr">
+      <c r="FZ1" s="0" t="inlineStr">
         <is>
           <t>robis_overall_explanation</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:177">
+    <row r="2" spans="1:182">
       <c r="A2" s="0">
         <v>6</v>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>Kiran, et al 2023 </t>
+          <t>Kiran, et al 2024 </t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
@@ -990,717 +1015,749 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>Three NIHR (National Institute for Health and Care Research) Research Schools Mental Health Programme Fellowship (Award MH010) and Global Challenges Funds Pump Priming Award</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
           <t>Cochrane Central Register of Controlled Trials (CENTRAL), Medline, PsycInfo, ClinicalTrials.gov, OpenTrials.net</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>2021_04</t>
         </is>
       </c>
-      <c r="L2" s="0" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="M2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N2" s="0" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O2" s="0" t="inlineStr">
+        <is>
           <t>CRD42020208723</t>
         </is>
       </c>
-      <c r="O2" s="0" t="inlineStr">
+      <c r="P2" s="0" t="inlineStr">
         <is>
           <t>Data are readily available upon request.</t>
         </is>
       </c>
-      <c r="P2" s="0" t="inlineStr">
+      <c r="Q2" s="0" t="inlineStr">
         <is>
           <t>Included studies involved children and young people aged between 12 and 25 years from any sociodemographic background, or staff members in educational settings working with young people aged between 12 and 25 years.</t>
         </is>
       </c>
-      <c r="Q2" s="0" t="inlineStr">
+      <c r="R2" s="0" t="inlineStr">
         <is>
           <t>Included: universal interventions (i.e., targeting the entire population of youngpeople or staff members at educational settings), selective interventions (i.e., targeting young people at high risk or educational or health care staff members at educational settings dealing with young people at risk) and indicated interventions (i.e., targeting young people already exhibiting high risk for suicide). Key intervention contents included education and/or awareness of suicide risk in young people, gatekeeper suicide prevention training of educational staff that involves the identification and referral of the at-risk young people (Cross et al., 2011), improved screening of young people for suicide risk by health care professionals, and psychotherapies</t>
         </is>
       </c>
-      <c r="R2" s="0" t="inlineStr">
+      <c r="S2" s="0" t="inlineStr">
         <is>
           <t>Include: Contained comparator groups such as no treatment, waiting list control, minimal intervention such as information provision and referral to community services (e.g., healthcare centers), usual care (UC), or fully active interventions.</t>
         </is>
       </c>
-      <c r="S2" s="0" t="inlineStr">
+      <c r="T2" s="0" t="inlineStr">
         <is>
           <t>Include: primary outcome data on STBs (e.g., suicide attempts, suicidal behaviors,or suicidal ideation) at postintervention or suicide prevention competencies (suicide-related knowledge, help-seeking skills, and attitudes) at postintervention. Other secondary outcomes included depression, anxiety, and hopelessness</t>
         </is>
       </c>
-      <c r="T2" s="0" t="inlineStr">
+      <c r="U2" s="0" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="U2" s="0" t="inlineStr">
+      <c r="V2" s="0" t="inlineStr">
         <is>
           <t>Include: Were based at schools, colleges, and universities of any country.</t>
         </is>
       </c>
-      <c r="V2" s="0" t="inlineStr">
+      <c r="W2" s="0" t="inlineStr">
         <is>
           <t>Include: Employed controlled intervention research designs including randomized controlled trials (RCTs), cluster RCTs, crossover trials, controlled before–after studies, and quasi-experimental study designs.</t>
         </is>
       </c>
-      <c r="W2" s="0" t="inlineStr">
+      <c r="X2" s="0" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
       </c>
-      <c r="X2" s="0" t="inlineStr">
+      <c r="Y2" s="0" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
-      <c r="AA2" s="0" t="inlineStr">
+      <c r="AB2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC2" s="0" t="inlineStr">
+        <is>
+          <t>RoB 2.0 for RCTs, ROBINS-I for NRSs; sensitivity analysis of ratings</t>
+        </is>
+      </c>
+      <c r="AD2" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE2" s="0" t="inlineStr">
+        <is>
+          <t>- Done by one reviewer and checked by a second.  - Used an overall numerical summary score for RoB 2.0 (from 0 to 6) rather than overall decision (low, some concerns, high) but in overall results did report % high and % low risk. Collapsed low/moderate to "low" and serious/critical to "high" for ROBINS-I (see appendix) - Differs from protocol, which did not have ROBINS-I, mentioned a third reviewer to manage disagreements, and did not mention the meta-regression by study quality: "The quality of the individual studies will be assessed independently by one reviewer using the Cochrane risk of bias tool for RCTs and observational intervention studies and checked by a second reviewer. Disagreements will be resolved by discussion and if necessary a third reviewer will be consulted." - Analyses: A sensitivity analysis on the quality of the studies involved using the overall RoB scores for each RCT (classified as high RoB for scores ≤3, and low RoB for scores &gt;3), and the overall RoB scores for the observational studies using ROBINS-I (classified as high RoB if either “serious” or “critical” risk, and low RoB if “low” or “moderate” risk). This allowed for combining of the RCT and observational studies in a sensitivity analysis. NOTE DISCREPANCY WITH SUPPLEMENTAL MATERIAL 9 (WHERE HIGH &gt;3 AND LOW ≤3)</t>
+        </is>
+      </c>
+      <c r="AF2" s="0" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="AB2" s="0" t="inlineStr">
+      <c r="AG2" s="0" t="inlineStr">
         <is>
           <t>Intervention</t>
         </is>
       </c>
-      <c r="AC2" s="0" t="inlineStr">
+      <c r="AH2" s="0" t="inlineStr">
         <is>
           <t>Comparator group</t>
         </is>
       </c>
-      <c r="AD2" s="0" t="inlineStr">
+      <c r="AI2" s="0" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="AF2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG2" s="0" t="inlineStr">
+      <c r="AK2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL2" s="0" t="inlineStr">
         <is>
           <t>review questions</t>
         </is>
       </c>
-      <c r="AH2" s="0" t="inlineStr">
+      <c r="AM2" s="0" t="inlineStr">
         <is>
           <t>a search strategy</t>
         </is>
       </c>
-      <c r="AI2" s="0" t="inlineStr">
+      <c r="AN2" s="0" t="inlineStr">
         <is>
           <t>inclusion/exclusion criteria</t>
         </is>
       </c>
-      <c r="AJ2" s="0" t="inlineStr">
+      <c r="AO2" s="0" t="inlineStr">
         <is>
           <t>a risk of bias assessment</t>
         </is>
       </c>
-      <c r="AK2" s="0" t="inlineStr">
+      <c r="AP2" s="0" t="inlineStr">
         <is>
           <t>a meta-analysis/synthesis plan, if appropriate (in the protocol), and</t>
         </is>
       </c>
-      <c r="AL2" s="0" t="inlineStr">
+      <c r="AQ2" s="0" t="inlineStr">
         <is>
           <t>a plan for investigating causes of heterogeneity (in the protocol)</t>
         </is>
       </c>
-      <c r="AN2" s="0" t="inlineStr">
+      <c r="AS2" s="0" t="inlineStr">
         <is>
           <t>Lisa: It doesn't really explicitly say the methods were established in advance, but the protocol uses future tense and was published before the searches. Therefore, the protocol did come out before the review was conducted. The protocol mentions databases searched but not the search terms, so those may not have been established in advance. The manuscript differs from the protocol in that it includes more detail (e.g., search terms, inclusion criteria) but I did not count this as a deviation. The protocol has a research question about intervention effectiveness in low and middle income countries that is not addressed in the paper. This deviation is not directly mentioned but the discussion does say they didn't find references from low and middle income countries.
 Kasia: I didn't see them mention network meta-analysis in their protocol analysis plan.</t>
         </is>
       </c>
-      <c r="AO2" s="0" t="inlineStr">
+      <c r="AT2" s="0" t="inlineStr">
         <is>
           <t>Partial Yes</t>
         </is>
       </c>
-      <c r="AR2" s="0" t="inlineStr">
+      <c r="AW2" s="0" t="inlineStr">
         <is>
           <t>Lisa: They included both but did not explain why. Kasia: No explanation for including RCTs AND NRSI, but sensitivity analysis with RCTs only included.</t>
         </is>
       </c>
-      <c r="AS2" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AT2" s="0" t="inlineStr">
+      <c r="AX2" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY2" s="0" t="inlineStr">
         <is>
           <t>searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU2" s="0" t="inlineStr">
+      <c r="AZ2" s="0" t="inlineStr">
         <is>
           <t>provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AV2" s="0" t="inlineStr">
+      <c r="BA2" s="0" t="inlineStr">
         <is>
           <t>justified publication restrictions (e.g. language)</t>
         </is>
       </c>
-      <c r="AW2" s="0" t="inlineStr">
+      <c r="BB2" s="0" t="inlineStr">
         <is>
           <t>searched the reference lists/bibliographies of included studies</t>
         </is>
       </c>
-      <c r="AX2" s="0" t="inlineStr">
+      <c r="BC2" s="0" t="inlineStr">
         <is>
           <t>searched trial/study registries</t>
         </is>
       </c>
-      <c r="AY2" s="0" t="inlineStr">
+      <c r="BD2" s="0" t="inlineStr">
         <is>
           <t>where relevant, searched for grey literature</t>
         </is>
       </c>
-      <c r="AZ2" s="0" t="inlineStr">
+      <c r="BE2" s="0" t="inlineStr">
         <is>
           <t>conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA2" s="0" t="inlineStr">
+      <c r="BF2" s="0" t="inlineStr">
         <is>
           <t>Lisa: No language or publication type restriction. Search was completed within 24months of submission of the review but not 24 months of publication of the review. The search terms seem like they could have included "intervention" or "program." Kasia: No language restriction at the search level. Search strategy in the supplement. No indication of expert consultation or explicit attempt to capture grey literature.</t>
         </is>
       </c>
-      <c r="BB2" s="0" t="inlineStr">
+      <c r="BG2" s="0" t="inlineStr">
         <is>
           <t>Partial Yes</t>
         </is>
       </c>
-      <c r="BC2" s="0" t="inlineStr">
+      <c r="BH2" s="0" t="inlineStr">
         <is>
           <t>at least two reviewers independently agreed on selection of eligible studies and achieved consensus on which studies to include</t>
         </is>
       </c>
-      <c r="BF2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BG2" s="0" t="inlineStr">
+      <c r="BK2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BL2" s="0" t="inlineStr">
         <is>
           <t>at least two reviewers achieved consensus on which data to extract from included studies</t>
         </is>
       </c>
-      <c r="BH2" s="0" t="inlineStr">
+      <c r="BM2" s="0" t="inlineStr">
         <is>
           <t>Lisa: They say data were extracted by two people but not what the consensus process was.</t>
         </is>
       </c>
-      <c r="BI2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BJ2" s="0" t="inlineStr">
+      <c r="BN2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO2" s="0" t="inlineStr">
         <is>
           <t>Lisa: No, and the number of full-texts screened minus the number excluded also doesn't match up to the number included. Kasia: I don't see a list anywhere, including the supplement.</t>
         </is>
       </c>
-      <c r="BK2" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BL2" s="0" t="inlineStr">
+      <c r="BP2" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ2" s="0" t="inlineStr">
         <is>
           <t>described populations</t>
         </is>
       </c>
-      <c r="BM2" s="0" t="inlineStr">
+      <c r="BR2" s="0" t="inlineStr">
         <is>
           <t>described interventions</t>
         </is>
       </c>
-      <c r="BN2" s="0" t="inlineStr">
+      <c r="BS2" s="0" t="inlineStr">
         <is>
           <t>described comparators</t>
         </is>
       </c>
-      <c r="BO2" s="0" t="inlineStr">
+      <c r="BT2" s="0" t="inlineStr">
         <is>
           <t>described outcomes</t>
         </is>
       </c>
-      <c r="BP2" s="0" t="inlineStr">
+      <c r="BU2" s="0" t="inlineStr">
         <is>
           <t>described research designs</t>
         </is>
       </c>
-      <c r="BS2" s="0" t="inlineStr">
+      <c r="BX2" s="0" t="inlineStr">
         <is>
           <t>described study's setting</t>
         </is>
       </c>
-      <c r="BU2" s="0" t="inlineStr">
+      <c r="BZ2" s="0" t="inlineStr">
         <is>
           <t>Lisa: Not a lot of detail on the populations. Only described STB outcomes, not all outcomes. Kasia: I don't see information about follow-up timeframe</t>
         </is>
       </c>
-      <c r="BV2" s="0" t="inlineStr">
+      <c r="CA2" s="0" t="inlineStr">
         <is>
           <t>Partial Yes</t>
         </is>
       </c>
-      <c r="BW2" s="0" t="inlineStr">
+      <c r="CB2" s="0" t="inlineStr">
         <is>
           <t>unconcealed allocation, and</t>
         </is>
       </c>
-      <c r="BX2" s="0" t="inlineStr">
+      <c r="CC2" s="0" t="inlineStr">
         <is>
           <t>lack of blinding of patients and assessors when assessing outcomes (unnecessary for objective outcomes such as all cause mortality)</t>
         </is>
       </c>
-      <c r="BY2" s="0" t="inlineStr">
+      <c r="CD2" s="0" t="inlineStr">
         <is>
           <t>allocation sequence that was not truly random, and</t>
         </is>
       </c>
-      <c r="BZ2" s="0" t="inlineStr">
+      <c r="CE2" s="0" t="inlineStr">
         <is>
           <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CA2" s="0" t="inlineStr">
+      <c r="CF2" s="0" t="inlineStr">
         <is>
           <t>Cochrane Risk of bias Tool 2.0 for the RCTs</t>
         </is>
       </c>
-      <c r="CB2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CC2" s="0" t="inlineStr">
+      <c r="CG2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CH2" s="0" t="inlineStr">
         <is>
           <t>confounding, and</t>
         </is>
       </c>
-      <c r="CD2" s="0" t="inlineStr">
+      <c r="CI2" s="0" t="inlineStr">
         <is>
           <t>selection bias</t>
         </is>
       </c>
-      <c r="CE2" s="0" t="inlineStr">
+      <c r="CJ2" s="0" t="inlineStr">
         <is>
           <t>methods used to ascertain exposures and outcomes, and</t>
         </is>
       </c>
-      <c r="CF2" s="0" t="inlineStr">
+      <c r="CK2" s="0" t="inlineStr">
         <is>
           <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CH2" s="0" t="inlineStr">
+      <c r="CM2" s="0" t="inlineStr">
         <is>
           <t>ROBINS-I</t>
         </is>
       </c>
-      <c r="CI2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CJ2" s="0" t="inlineStr">
+      <c r="CN2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CO2" s="0" t="inlineStr">
         <is>
           <t>No information about funding for included studies</t>
         </is>
       </c>
-      <c r="CK2" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CL2" s="0" t="inlineStr">
+      <c r="CP2" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CQ2" s="0" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM2" s="0" t="inlineStr">
+      <c r="CR2" s="0" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN2" s="0" t="inlineStr">
+      <c r="CS2" s="0" t="inlineStr">
         <is>
           <t>AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO2" s="0" t="inlineStr">
+      <c r="CT2" s="0" t="inlineStr">
         <is>
           <t>network meta-analysis; multiple subgroup effects analysed; heterogeneity stats reported</t>
         </is>
       </c>
-      <c r="CP2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CQ2" s="0" t="inlineStr">
+      <c r="CU2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CV2" s="0" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CR2" s="0" t="inlineStr">
+      <c r="CW2" s="0" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results, adjusting for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CS2" s="0" t="inlineStr">
+      <c r="CX2" s="0" t="inlineStr">
         <is>
           <t>AND they statistically combined effect estimates from NRSI that were adjusted for confounding, rather than combining raw data, or justified combining raw data when adjusted effect estimates were not available</t>
         </is>
       </c>
-      <c r="CU2" s="0" t="inlineStr">
+      <c r="CZ2" s="0" t="inlineStr">
         <is>
           <t>Lisa: They did a sensitivity analysis removing the non-randomized studies. They report RCTs on their own but not NRSI on their own.. Kasia: network meta-analysis; multiple subgroup effects analysed; heterogeneity stats reported; results for combined designs and RCTs-only reported; I did not see discussion of adjusting for confounding for NRSIs, but maybe it's a part of random-effects network MA by definition (?)</t>
         </is>
       </c>
-      <c r="CV2" s="0" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CW2" s="0" t="inlineStr">
+      <c r="DA2" s="0" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DB2" s="0" t="inlineStr">
         <is>
           <t>OR, if the pooled estimate was based on RCTs and/or NRSI at variable RoB, the authors performed analyses to investigate possible impact of RoB on summary estimates of effect</t>
         </is>
       </c>
-      <c r="CX2" s="0" t="inlineStr">
+      <c r="DC2" s="0" t="inlineStr">
         <is>
           <t>Lisa: In supplement. Kasia: Separate analyses for combined designs and RCTs only; also, meta-regressions in the supplement included results for low versus high RoB studies.</t>
         </is>
       </c>
-      <c r="CY2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CZ2" s="0" t="inlineStr">
+      <c r="DD2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DE2" s="0" t="inlineStr">
         <is>
           <t>OR, if RCTs with moderate or high RoB, or NRSI were included the review provided a discussion of the likely impact of RoB on the results</t>
         </is>
       </c>
-      <c r="DA2" s="0" t="inlineStr">
+      <c r="DF2" s="0" t="inlineStr">
         <is>
           <t>Lisa: They did statistically compare high and low risk studies and mentions interpreting results with caution due to low quality evidence. Kasia: Study quality mentioned in the limitations section.</t>
         </is>
       </c>
-      <c r="DB2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DD2" s="0" t="inlineStr">
+      <c r="DG2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DI2" s="0" t="inlineStr">
         <is>
           <t>OR if heterogeneity was present the authors performed an investigation of sources of any heterogeneity in the results and discussed the impact of this on the results of the review</t>
         </is>
       </c>
-      <c r="DE2" s="0" t="inlineStr">
+      <c r="DJ2" s="0" t="inlineStr">
         <is>
           <t>Lisa: They did appropriate analyses of heterogeneity and mentioned it in the discussion. They did a lot of comparisons in the supplement, that are discussed and would potentially explain some of the heterogeneity. Kasia: Various subgroup analyses and moderator analyses conducted. Results for different subgroups addressed in the discussion section.</t>
         </is>
       </c>
-      <c r="DF2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DG2" s="0" t="inlineStr">
+      <c r="DK2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DL2" s="0" t="inlineStr">
         <is>
           <t>performed graphical or statistical tests for publication bias and discussed the likelihood and magnitude of impact of publication bias</t>
         </is>
       </c>
-      <c r="DH2" s="0" t="inlineStr">
+      <c r="DM2" s="0" t="inlineStr">
         <is>
           <t>Publication bias assessed (Egger's tests) and discussed in the limitations section.</t>
         </is>
       </c>
-      <c r="DI2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DJ2" s="0" t="inlineStr">
+      <c r="DN2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DO2" s="0" t="inlineStr">
         <is>
           <t>The authors reported no competing interests OR</t>
         </is>
       </c>
-      <c r="DK2" s="0" t="inlineStr">
+      <c r="DP2" s="0" t="inlineStr">
         <is>
           <t>The authors described their funding sources and how they managed potential conflicts of interest</t>
         </is>
       </c>
-      <c r="DL2" s="0" t="inlineStr">
+      <c r="DQ2" s="0" t="inlineStr">
         <is>
           <t>Lisa: It sounds like the funders did not influence the project method and results. Kasia: Authors declared no conflicts of interest.</t>
         </is>
       </c>
-      <c r="DM2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DN2" s="0" t="inlineStr">
+      <c r="DR2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DS2" s="0" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DO2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Critical weakness with item 7. They did explain why they excluded different numbers of studies but did not provide a list. Kasia: No justification/list of excluded individual studies. Otherwise, no major concerns about this review.</t>
-        </is>
-      </c>
-      <c r="DP2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DQ2" s="0" t="inlineStr">
+      <c r="DT2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Critical weakness with item 7. They did explain why they excluded different numbers of studies but did not provide a list. Kasia: No justification/list of excluded individual studies. Otherwise, no major concerns about this review.
+Lisa and Sean discussion: Not downgraded to critically low based on item 11 due to only 3 NRSI in the STB network, RCT-only sensitivity analyses unchanged, concern acknowledged in review's limitations</t>
+        </is>
+      </c>
+      <c r="DU2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DV2" s="0" t="inlineStr">
         <is>
           <t>Lisa: Mostly. They had an objective about low and middle income countries, but since they did not find studies from those countries, that question would have been difficult to address. The methods were also more detailed in the paper than the protocol, as the protocol did not include specific search terms.</t>
         </is>
       </c>
-      <c r="DR2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DT2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DV2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="DW2" s="0" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DY2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EB2" s="0" t="inlineStr">
+        <is>
           <t>Lisa: They didn't really have restrictions.</t>
         </is>
       </c>
-      <c r="DX2" s="0" t="inlineStr">
+      <c r="EC2" s="0" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="ED2" s="0" t="inlineStr">
+        <is>
+          <t>Kasia: Language restriction for eligibility. Only peer-reviewed articles included. 
+Explanation for restrictions not provided.</t>
+        </is>
+      </c>
+      <c r="EE2" s="0" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="EF2" s="0" t="inlineStr">
+        <is>
+          <t>Kasia: Grey literature excluded (only peer-reviewed, published articles included).</t>
+        </is>
+      </c>
+      <c r="EG2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EH2" s="0" t="inlineStr">
+        <is>
+          <t>Kasia: 3 major databases + trial registries</t>
+        </is>
+      </c>
+      <c r="EI2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ2" s="0" t="inlineStr">
+        <is>
+          <t>Kasia: Citation chasing</t>
+        </is>
+      </c>
+      <c r="EK2" s="0" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DY2" s="0" t="inlineStr">
-        <is>
-          <t>Kasia: Language restriction for eligibility. Only peer-reviewed articles included.</t>
-        </is>
-      </c>
-      <c r="DZ2" s="0" t="inlineStr">
+      <c r="EL2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: The strategy looks pretty good but I think they likely should have included theterms "intervention" and "program."</t>
+        </is>
+      </c>
+      <c r="EM2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EN2" s="0" t="inlineStr">
+        <is>
+          <t>No language restrictions at the search level.  Publication type not reported to be restricted at the search level.</t>
+        </is>
+      </c>
+      <c r="EO2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EQ2" s="0" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="EA2" s="0" t="inlineStr">
-        <is>
-          <t>Kasia: Grey literature excluded (only peer-reviewed, published articles included).</t>
-        </is>
-      </c>
-      <c r="EB2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EC2" s="0" t="inlineStr">
-        <is>
-          <t>Kasia: 3 major databases + trial registries</t>
-        </is>
-      </c>
-      <c r="ED2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EE2" s="0" t="inlineStr">
-        <is>
-          <t>Kasia: Citation chasing</t>
-        </is>
-      </c>
-      <c r="EF2" s="0" t="inlineStr">
+      <c r="ES2" s="0" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EG2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: The strategy looks pretty good but I think they likely should have included theterms "intervention" and "program."</t>
-        </is>
-      </c>
-      <c r="EH2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EI2" s="0" t="inlineStr">
-        <is>
-          <t>No language restrictions at the search level.  Publication type not reported to be restricted at the search level.</t>
-        </is>
-      </c>
-      <c r="EJ2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EL2" s="0" t="inlineStr">
+      <c r="ET2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Collected in duplicate, although they do not explain how discrepancies were reconciled</t>
+        </is>
+      </c>
+      <c r="EU2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EW2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EY2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FA2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FB2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Double checked by a second reviewer.</t>
+        </is>
+      </c>
+      <c r="FC2" s="0" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="EN2" s="0" t="inlineStr">
+      <c r="FE2" s="0" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EO2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Collected in duplicate, although they do not explain how discrepancies were reconciled</t>
-        </is>
-      </c>
-      <c r="EP2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ER2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ET2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EV2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EW2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Double checked by a second reviewer.</t>
-        </is>
-      </c>
-      <c r="EX2" s="0" t="inlineStr">
+      <c r="FF2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Thompson 2001 in the supplemental table of included studies does not appear to be in any of the forest plots in the supplement. The NMA figures don't have individual author names, so it is hard to tell if it is in that analysis. Unclear why this was not analyzed. It is also not in the citation list of included studies, so it's possible it should not have been in the table of included studies.</t>
+        </is>
+      </c>
+      <c r="FG2" s="0" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="FH2" s="0" t="inlineStr">
+        <is>
+          <t>Kasia: Protocol not detailed enough to judge if there were major departures. No explicit departures or explanations reported. Lisa: The protocol says they'll analyze controlled and uncontrolled studies separately. They did a sensitivity analysis removing non randomized ones, but didn't report those separately. Otherwise they followed the protocol but did more detailed/additional things in the paper.</t>
+        </is>
+      </c>
+      <c r="FI2" s="0" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="FJ2" s="0" t="inlineStr">
+        <is>
+          <t>They report RCTs on their own but not NRSI on their own. Kasia: network meta-analysis; multiple subgroup effects analysed; heterogeneity stats reported; results for combined designs and RCTs-only reported; I did not see discussion of adjusting for confounding for NRSIs, but maybe it's a part of random-effects network MA by definition (?)</t>
+        </is>
+      </c>
+      <c r="FK2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FM2" s="0" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="FN2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Publication bias reported, but sensitivity analyses not always done/reported.</t>
+        </is>
+      </c>
+      <c r="FO2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FP2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: There were lots of critical risk primary studies, but they did analyze high vs low quality data.</t>
+        </is>
+      </c>
+      <c r="FQ2" s="0" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="EZ2" s="0" t="inlineStr">
+      <c r="FR2" s="0" t="inlineStr">
+        <is>
+          <t>Lisa: Unclear if there was a reason for one study not being in analyses, and unclear effect of publication bias on the results.</t>
+        </is>
+      </c>
+      <c r="FS2" s="0" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FA2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Thompson 2001 in the supplemental table of included studies does not appear to be in any of the forest plots in the supplement. The NMA figures don't have individual author names, so it is hard to tell if it is in that analysis. Unclear why this was not analyzed. It is also not in the citation list of included studies, so it's possible it should not have been in the table of included studies.</t>
-        </is>
-      </c>
-      <c r="FB2" s="0" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FC2" s="0" t="inlineStr">
-        <is>
-          <t>Kasia: Protocol not detailed enough to judge if there were major departures. No explicit departures or explanations reported. Lisa: The protocol says they'll analyze controlled and uncontrolled studies separately. They did a sensitivity analysis removing non randomized ones, but didn't report those separately. Otherwise they followed the protocol but did more detailed/additional things in the paper.</t>
-        </is>
-      </c>
-      <c r="FD2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FF2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FH2" s="0" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FI2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Publication bias reported, but sensitivity analyses not always done/reported.</t>
-        </is>
-      </c>
-      <c r="FJ2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FK2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: There were lots of critical risk primary studies, but they did analyze high vs low quality data.</t>
-        </is>
-      </c>
-      <c r="FL2" s="0" t="inlineStr">
+      <c r="FU2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FW2" s="0" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY2" s="0" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="FM2" s="0" t="inlineStr">
-        <is>
-          <t>Lisa: Unclear if there was a reason for one study not being in analyses, and unclear effect of publication bias on the results.</t>
-        </is>
-      </c>
-      <c r="FN2" s="0" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FP2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FR2" s="0" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FT2" s="0" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="FU2" s="0" t="inlineStr">
+      <c r="FZ2" s="0" t="inlineStr">
         <is>
           <t>Lisa: I was somewhat on the fence here. Some aspects were slightly less than ideal (e.g., search terms not in the protocol), but nothing seems like it would lead to severe bias, and interpretations seem reasonable.</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:177">
+    <row r="3" spans="1:182">
       <c r="A3" s="1">
         <v>11</v>
       </c>
@@ -1741,707 +1798,732 @@
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
+          <t>This study was funded by Trimbos Institute and GGZ Oost Brabant. GGZ Oost Brabant received funding from the municipalities of Asten, Deurne, Geldrop-Mierlo, Gemert-Bakel, Helmond, Laarbeek, and Someren.</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>Medline, PsycInfo, Cochrane Central Register of Controlled Trials, EMBASE</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N3" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr">
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="P3" s="1" t="inlineStr">
+      <c r="Q3" s="1" t="inlineStr">
         <is>
           <t>Include: the participants were children or adolescents up to the age of 25, but studies did not only include participants older than 18 years. (Note that the studies they actually found only went up to HS at the oldest.)</t>
         </is>
       </c>
-      <c r="Q3" s="1" t="inlineStr">
+      <c r="R3" s="1" t="inlineStr">
         <is>
           <t>The authors do not list intervention criteria in the inclusion/exclusion criteria section. However, the intro states "the current review and meta-analysis will not be restricted to studies that aim to reduce suicidality, but will include all studies that have included STBs as an outcome measurement to explore potential effects of studies that target risk factors of STBs. As such, the current meta-analyses aims to review the literature to identify and analyze effectiveness of school-based preventive strategies on STBs."</t>
         </is>
       </c>
-      <c r="R3" s="1" t="inlineStr">
+      <c r="S3" s="1" t="inlineStr">
         <is>
           <t>Include: control group who received either no intervention, placebo, or usual care. Note that the exclusion criteria do not mention studies without a control group, but the results mention excluding studies without a control group.</t>
         </is>
       </c>
-      <c r="S3" s="1" t="inlineStr">
+      <c r="T3" s="1" t="inlineStr">
         <is>
           <t>Include: the outcome of the study included a measure of suicidal thoughts and behaviors. The results mention excluding/not analyzing studies that do not look at suicidal thoughts and behaviors, such as ones that only looked at attitudes toward suicide or help-seeking intentions.</t>
         </is>
       </c>
-      <c r="T3" s="1" t="inlineStr">
+      <c r="U3" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="U3" s="1" t="inlineStr">
+      <c r="V3" s="1" t="inlineStr">
         <is>
           <t>Include: school setting</t>
         </is>
       </c>
-      <c r="V3" s="1" t="inlineStr">
+      <c r="W3" s="1" t="inlineStr">
         <is>
           <t>Include: assignment of individuals to the intervention and control groups in included studies was random (i.e. conducted as a randomized controlled trial); published in the English or Dutch language; the data are reported such that effect sizes could be computed; studies were using original data. Note that the exclusion criteria do not mention non-randomized designs, but the results mention excluding non-randomized studies.</t>
         </is>
       </c>
-      <c r="W3" s="1" t="inlineStr">
+      <c r="X3" s="1" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
       </c>
-      <c r="X3" s="1" t="inlineStr">
+      <c r="Y3" s="1" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
-      <c r="Z3" s="1" t="inlineStr">
+      <c r="AA3" s="1" t="inlineStr">
         <is>
           <t>School settings</t>
         </is>
       </c>
-      <c r="AA3" s="1" t="inlineStr">
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC3" s="1" t="inlineStr">
+        <is>
+          <t>Cochrane Risk of Bias tool for cluster randomized trials (modified to omit blinding); citation indicates RoB 2.0</t>
+        </is>
+      </c>
+      <c r="AD3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE3" s="1" t="inlineStr">
+        <is>
+          <t>- Excluded blinding of participants and personnel: "We decided to exclude the risk-of-bias criterion Blinding of participants and personnel, because in psychological interventions blinding of participants and personnel is not feasible. Also, most studies used self-report measurements and this renders any blinding of the outcome assessors impossible. Previous studies showed that using self-report measures does not lead to inflated effect sizes, but could lead to more conservative estimates (Cuijpers et al., 2010)." - Used the Cochrane tool for cluster-randomized studies but may have included some studies randomized at individual level. Eligibility criterion: "assignment of individuals to the intervention and control groups in included studies was random" - Assessed in duplicate but not 100% clear how risk of bias assessment conflicts were resolved. Data extraction reconciliation process is described as cross-checking for accuracy by both reviewers, but unclear of risk of bias assessment is considered data extraction. - No overall RoB assessment reported, only domain-level - Multivariate meta-regression analyses were performed in StataSE 16 to evaluate if quality of the primary studies is systematically covarying with the size of the study’s effect size. In light of previous experience, it was expected that studies with higher quality would be associated with smaller effect sizes.</t>
+        </is>
+      </c>
+      <c r="AF3" s="1" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="AB3" s="1" t="inlineStr">
+      <c r="AG3" s="1" t="inlineStr">
         <is>
           <t>Intervention</t>
         </is>
       </c>
-      <c r="AC3" s="1" t="inlineStr">
+      <c r="AH3" s="1" t="inlineStr">
         <is>
           <t>Comparator group</t>
         </is>
       </c>
-      <c r="AD3" s="1" t="inlineStr">
+      <c r="AI3" s="1" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="AE3" s="1" t="inlineStr">
+      <c r="AJ3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They do mention PICOS. The intervention description provided is more of a setting "the preventive intervention was offered in the school setting (I)" The criteria for the type of intervention is not clear (e.g., what does it have to target).</t>
         </is>
       </c>
-      <c r="AF3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AN3" s="1" t="inlineStr">
+      <c r="AK3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AS3" s="1" t="inlineStr">
         <is>
           <t>Lisa: No protocol mentioned. Andrew: Reviewers state that the study is reported in line with PRISMA guidelines, which recommend that authors clarify that they are working from a protocol, but do not directly acknowledge use of a protocol.</t>
         </is>
       </c>
-      <c r="AO3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AR3" s="1" t="inlineStr">
+      <c r="AT3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Included only RCTs but no explanation. Andrew: The review includes only RCTs; the authors did not proffer an explanation for this criterion.</t>
         </is>
       </c>
-      <c r="AS3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AT3" s="1" t="inlineStr">
+      <c r="AX3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY3" s="1" t="inlineStr">
         <is>
           <t>searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU3" s="1" t="inlineStr">
+      <c r="AZ3" s="1" t="inlineStr">
         <is>
           <t>provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AV3" s="1" t="inlineStr">
+      <c r="BA3" s="1" t="inlineStr">
         <is>
           <t>justified publication restrictions (e.g. language)</t>
         </is>
       </c>
-      <c r="AW3" s="1" t="inlineStr">
+      <c r="BB3" s="1" t="inlineStr">
         <is>
           <t>searched the reference lists/bibliographies of included studies</t>
         </is>
       </c>
-      <c r="AX3" s="1" t="inlineStr">
+      <c r="BC3" s="1" t="inlineStr">
         <is>
           <t>searched trial/study registries</t>
         </is>
       </c>
-      <c r="AY3" s="1" t="inlineStr">
+      <c r="BD3" s="1" t="inlineStr">
         <is>
           <t>where relevant, searched for grey literature</t>
         </is>
       </c>
-      <c r="AZ3" s="1" t="inlineStr">
+      <c r="BE3" s="1" t="inlineStr">
         <is>
           <t>conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA3" s="1" t="inlineStr">
+      <c r="BF3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They had unjustified restrictions at the study selection stage but not the screening stage. They say they searched the reference lists of reviews they identified, but it is not clear if they searched the reference lists of included studies. Unclear when the search was conducted. No specific mention of grey literature, but I gave them credit since their databases seem like they may have returned some. Andrew: Included studies are restricted to those published in English or Dutch. This presumably reflects the authors' fluency, but no justification is given. Authors do not provide exact date of final search, but date range of studies extends to Feb. 2020 and a revised draft of the paper was accepted in Oct. 2021; it is thus implied that the search occurred within 24 months of review completion.</t>
         </is>
       </c>
-      <c r="BB3" s="1" t="inlineStr">
+      <c r="BG3" s="1" t="inlineStr">
         <is>
           <t>Partial Yes</t>
         </is>
       </c>
-      <c r="BC3" s="1" t="inlineStr">
+      <c r="BH3" s="1" t="inlineStr">
         <is>
           <t>at least two reviewers independently agreed on selection of eligible studies and achieved consensus on which studies to include</t>
         </is>
       </c>
-      <c r="BE3" s="1" t="inlineStr">
+      <c r="BJ3" s="1" t="inlineStr">
         <is>
           <t>Unclear if titles and abstracts were screened in duplicate or only full texts "title and abstract were scanned to see if they met inclusion criteria; when this could not be determined from title and abstract alone, full-texts were retrieved and reviewed in their entirety and independently by two of the authors (MG and SR) to determine whether they met inclusion criteria. All discrepancies between MG and SR were discussed until consensus was reached."</t>
         </is>
       </c>
-      <c r="BF3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BG3" s="1" t="inlineStr">
+      <c r="BK3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BL3" s="1" t="inlineStr">
         <is>
           <t>at least two reviewers achieved consensus on which data to extract from included studies</t>
         </is>
       </c>
-      <c r="BH3" s="1" t="inlineStr">
+      <c r="BM3" s="1" t="inlineStr">
         <is>
           <t>"Data were extracted independently by two reviewers (MG and SR) using a standardized data format and subsequently cross-checked for accuracy by both reviewers. After verification of the extracted data all 
 discrepancies were discussed until consensus was reached. The inter-rater agreement between the two reviewers was 93%."</t>
         </is>
       </c>
-      <c r="BI3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BJ3" s="1" t="inlineStr">
+      <c r="BN3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO3" s="1" t="inlineStr">
         <is>
           <t>Lisa: The PRISMA chart has counts of articles excluded for different reasons but there is no list with specific references and the reason for excluding each. Andrew: No list of excluded studies is provided.</t>
         </is>
       </c>
-      <c r="BK3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BL3" s="1" t="inlineStr">
+      <c r="BP3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ3" s="1" t="inlineStr">
         <is>
           <t>described populations</t>
         </is>
       </c>
-      <c r="BM3" s="1" t="inlineStr">
+      <c r="BR3" s="1" t="inlineStr">
         <is>
           <t>described interventions</t>
         </is>
       </c>
-      <c r="BN3" s="1" t="inlineStr">
+      <c r="BS3" s="1" t="inlineStr">
         <is>
           <t>described comparators</t>
         </is>
       </c>
-      <c r="BO3" s="1" t="inlineStr">
+      <c r="BT3" s="1" t="inlineStr">
         <is>
           <t>described outcomes</t>
         </is>
       </c>
-      <c r="BP3" s="1" t="inlineStr">
+      <c r="BU3" s="1" t="inlineStr">
         <is>
           <t>described research designs</t>
         </is>
       </c>
-      <c r="BS3" s="1" t="inlineStr">
+      <c r="BX3" s="1" t="inlineStr">
         <is>
           <t>described study's setting</t>
         </is>
       </c>
-      <c r="BT3" s="1" t="inlineStr">
+      <c r="BY3" s="1" t="inlineStr">
         <is>
           <t>timeframe for follow-up</t>
         </is>
       </c>
-      <c r="BU3" s="1" t="inlineStr">
+      <c r="BZ3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Did not really describe research designs but only included RCTs, so did not need to I suppose. Andrew: Populations are described in terms of age and gender distribution. Interventions are named; providers and primary outcomes are identified. Research designs and settings are uniformly RCTs and schools (respectively) as stipulated by inclusion criteria</t>
         </is>
       </c>
-      <c r="BV3" s="1" t="inlineStr">
+      <c r="CA3" s="1" t="inlineStr">
         <is>
           <t>Partial Yes</t>
         </is>
       </c>
-      <c r="BW3" s="1" t="inlineStr">
+      <c r="CB3" s="1" t="inlineStr">
         <is>
           <t>unconcealed allocation, and</t>
         </is>
       </c>
-      <c r="BY3" s="1" t="inlineStr">
+      <c r="CD3" s="1" t="inlineStr">
         <is>
           <t>allocation sequence that was not truly random, and</t>
         </is>
       </c>
-      <c r="BZ3" s="1" t="inlineStr">
+      <c r="CE3" s="1" t="inlineStr">
         <is>
           <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CA3" s="1" t="inlineStr">
+      <c r="CF3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used RoB 2. The authors explain "We decided to exclude the risk-of-bias criterion Blinding of participants and personnel, because in psychology". Andrew: Reviewers used Cochrane RoB tool, excluded blinding of participants and personnel because "in psychological interventions blinding of participants and personnel is not feasible."</t>
         </is>
       </c>
-      <c r="CB3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="CG3" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CL3" s="1" t="inlineStr">
+        <is>
           <t>Includes only RCT</t>
         </is>
       </c>
-      <c r="CI3" s="1" t="inlineStr">
+      <c r="CN3" s="1" t="inlineStr">
         <is>
           <t>Includes only RCTs</t>
         </is>
       </c>
-      <c r="CJ3" s="1" t="inlineStr">
+      <c r="CO3" s="1" t="inlineStr">
         <is>
           <t>The authors did not report on individual study funding sources, nor did they report looking for this information.</t>
         </is>
       </c>
-      <c r="CK3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CL3" s="1" t="inlineStr">
+      <c r="CP3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CQ3" s="1" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM3" s="1" t="inlineStr">
+      <c r="CR3" s="1" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN3" s="1" t="inlineStr">
+      <c r="CS3" s="1" t="inlineStr">
         <is>
           <t>AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO3" s="1" t="inlineStr">
+      <c r="CT3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They don't explicitly say the data were okay to combine, but they explain how they dealt with different reporting in primary studies and including studies with multiple intervention arms. Kasia: The authors stated that meta-analyses within the review aimed to survey current literature and analyze effectiveness of school-based preventive strategies on suicidal thoughts and behaviors. Separate analyses were conducted for suicidal thoughts (ideation) and behaviors. The authors reported use of a (random effects) method of moments model, which presumably weighted studies and allowed for heterogeneity. The authors did not explain why they used this model.</t>
         </is>
       </c>
-      <c r="CP3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CT3" s="1" t="inlineStr">
+      <c r="CU3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY3" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CV3" s="1" t="inlineStr">
+      <c r="DA3" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CX3" s="1" t="inlineStr">
+      <c r="DC3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Most studies scored low on most aspects of RoB. Overall RoB not reported, just each subscale. I don't think they analyzed effects of RoB on the results, but they did do an analysis of study "quality" on page 414, but it is unclear what the quality variable was. Left out blinding for RoB. Andrew: One study was assessed as both high risk of selection bias and some risk of attrition bias and retained nonetheless; no analyses were conducted to investigate the possible impact of RoB on effect.</t>
         </is>
       </c>
-      <c r="CY3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DA3" s="1" t="inlineStr">
+      <c r="DD3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DF3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Most studies scored low on most aspects of RoB. They don't report on overall RoB, just each subscale, so it's unclear if one study that was high in one domain would have been counted as low or not. Discussion does not talk about RoB. They did evaluate publication bias. Andrew: Minimal discussion of individual study biases in discussing results, other than acknowledgment of use of single-item measure.</t>
         </is>
       </c>
-      <c r="DB3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DD3" s="1" t="inlineStr">
+      <c r="DG3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI3" s="1" t="inlineStr">
         <is>
           <t>OR if heterogeneity was present the authors performed an investigation of sources of any heterogeneity in the results and discussed the impact of this on the results of the review</t>
         </is>
       </c>
-      <c r="DE3" s="1" t="inlineStr">
+      <c r="DJ3" s="1" t="inlineStr">
         <is>
           <t>The authors observed significant heterogeneity, assessed possible sources of heterogeneity (namely: study quality, year of pub., and multimodal vs single preventive strategy) and found null results, and suggested in the discussion section that heterogeneous outcome measures might, in fact, represent slightly different constructs being examined on a per-study basis.</t>
         </is>
       </c>
-      <c r="DF3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DG3" s="1" t="inlineStr">
+      <c r="DK3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DL3" s="1" t="inlineStr">
         <is>
           <t>performed graphical or statistical tests for publication bias and discussed the likelihood and magnitude of impact of publication bias</t>
         </is>
       </c>
-      <c r="DH3" s="1" t="inlineStr">
+      <c r="DM3" s="1" t="inlineStr">
         <is>
           <t>The authors visually inspected a funnel plot and use trim and fill procedures for each analysis.</t>
         </is>
       </c>
-      <c r="DI3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DJ3" s="1" t="inlineStr">
+      <c r="DN3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DO3" s="1" t="inlineStr">
         <is>
           <t>The authors reported no competing interests OR</t>
         </is>
       </c>
-      <c r="DM3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DN3" s="1" t="inlineStr">
+      <c r="DR3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DS3" s="1" t="inlineStr">
         <is>
           <t>CRITICALLY LOW</t>
         </is>
       </c>
-      <c r="DO3" s="1" t="inlineStr">
+      <c r="DT3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Critical weaknesses on items 2 (protocol registration) and 7 (justification for excluding individual studies) and 9 (RoB might be present with respect to blinding but we are not sure). Potentially also concerns with RoB not being discussed thoroughly. Andrew: Critical weaknesses in domaines 2, 4, 7, 9, and 13.</t>
         </is>
       </c>
-      <c r="DP3" s="1" t="inlineStr">
+      <c r="DU3" s="1" t="inlineStr">
         <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="DQ3" s="1" t="inlineStr">
+      <c r="DV3" s="1" t="inlineStr">
         <is>
           <t>Lisa: No evidence of pre-specification. Andrew: No report of protocol</t>
         </is>
       </c>
-      <c r="DR3" s="1" t="inlineStr">
+      <c r="DW3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DS3" s="1" t="inlineStr">
+      <c r="DX3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They seemed appropriate. Not totally clear about the contents of the intervention (for the "I" in PICO, a school setting was described, not the focus of the intervention). Andrew: Eligibility criteria yielded appropriate studies, though no justification for excluding NRSIs.</t>
         </is>
       </c>
-      <c r="DT3" s="1" t="inlineStr">
+      <c r="DY3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DU3" s="1" t="inlineStr">
+      <c r="DZ3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used PICOS. Not totally clear about the contents of the intervention, but otherwise ok (for the "I" in PICO, just described prevention in a school setting, not the focus of the intervention).</t>
         </is>
       </c>
-      <c r="DV3" s="1" t="inlineStr">
+      <c r="EA3" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="DW3" s="1" t="inlineStr">
+      <c r="EB3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Inclusion of RCTs only was not justified. Outcomes seem appropriate.  Date search criteria were not justified but seem probably okay.</t>
         </is>
       </c>
-      <c r="DX3" s="1" t="inlineStr">
+      <c r="EC3" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="DY3" s="1" t="inlineStr">
+      <c r="ED3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified language restriction. No information on publication status or format. Andrew: Included studies were restricted to those published in English or Dutch. No rationale is given for either restriction (i.e. publication status and language); both are later mentioned as limitations of the review.</t>
         </is>
       </c>
-      <c r="DZ3" s="1" t="inlineStr">
+      <c r="EE3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EA3" s="1" t="inlineStr">
+      <c r="EF3" s="1" t="inlineStr">
         <is>
           <t>Lisa: No protocol, some unjustified restrictions, unclear intervention inclusion criteria. Andrew: High concern due to publication bias and language restriction; possibility of added concern due to no report of a protocol</t>
         </is>
       </c>
-      <c r="EB3" s="1" t="inlineStr">
+      <c r="EG3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EC3" s="1" t="inlineStr">
+      <c r="EH3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They do not mention specifically searching for grey literature but I think the databases they included could have returned some. Andrew: Authors searched an appropriate range of databases for published reports, as well as one trial registry database. Authors did not directly search for unpublished reports.</t>
         </is>
       </c>
-      <c r="ED3" s="1" t="inlineStr">
+      <c r="EI3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EE3" s="1" t="inlineStr">
+      <c r="EJ3" s="1" t="inlineStr">
         <is>
           <t>Lisa: They only mention searching review reference lists, not full reference checking, contacting experts, handsearching. Andrew: Reviewing reference lists of included studies.</t>
         </is>
       </c>
-      <c r="EF3" s="1" t="inlineStr">
+      <c r="EK3" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EG3" s="1" t="inlineStr">
+      <c r="EL3" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of database-specific  indexing terms. No terms related to population (children, adolescents). Not clear on reasons for groups of terms, e.g., the block with "educational programs" grouped separately from the block with "program*"</t>
         </is>
       </c>
-      <c r="EH3" s="1" t="inlineStr">
+      <c r="EM3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EI3" s="1" t="inlineStr">
+      <c r="EN3" s="1" t="inlineStr">
         <is>
           <t>Lisa: The date restriction seems probably reasonable to me  but is not justified by the authors. Andrew: No rationale given for restrictions based on publication format and language.</t>
         </is>
       </c>
-      <c r="EJ3" s="1" t="inlineStr">
+      <c r="EO3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EK3" s="1" t="inlineStr">
+      <c r="EP3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Full texts were double-screened but they do not explain whether title and abstracts were "Of the remaining articles, title and abstract were scanned to see if they met inclusion criteria; when this could not be determined from title and abstract alone, full-texts were retrieved and reviewed in their entirety and independently by two of the authors (MG and SR) to determine whether they met inclusion criteria. All discrepancies between MG and SR were discussed until consensus was reached."</t>
         </is>
       </c>
-      <c r="EL3" s="1" t="inlineStr">
+      <c r="EQ3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EM3" s="1" t="inlineStr">
+      <c r="ER3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Potential issues with search terms and no information about error minimization in title and abstract screening. Andrew: High risk of publication bias, as well as exclusion of 8 potentially relevant studies that were not published in English or Dutch.</t>
         </is>
       </c>
-      <c r="EN3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EO3" s="1" t="inlineStr">
+      <c r="ES3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="ET3" s="1" t="inlineStr">
         <is>
           <t>Lisa: "Data were extracted independently by two reviewers (MG and SR) using a standardized data format and subsequently cross-checked for accuracy by both reviewers."</t>
         </is>
       </c>
-      <c r="EP3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ER3" s="1" t="inlineStr">
+      <c r="EU3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EW3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="ES3" s="1" t="inlineStr">
+      <c r="EX3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Yes except they didn't worry about blinding since they say it is not possible in psychological studies. "We decided to exclude the risk-of-bias criterion Blinding of participants and personnel, because in psychological interventions blinding of participants and personnel is not feasible. Also, most studies used self-report measurements and this renders any blinding of the outcome assessors impossible". Andrew: Lisa: PRISMA chart indicates that some studies were excluded for not having usable data, but it is unclear if attempts were made to get data from authors. It seems likely they did not contact authors since an inclusion criteria was having data reported such that effect sizes could be computed. Andrew: Included studies needed to provide sufficient data for reviewers to calculate effect size. The authors describe how relative risk ratios were converted to odds ratios and, subsequently, to effect sizes.</t>
         </is>
       </c>
-      <c r="ET3" s="1" t="inlineStr">
+      <c r="EY3" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="EZ3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Yes except they didn't worry about blinding since they say it is not possible in psychological studies. "We decided to exclude the risk-of-bias criterion Blinding of participants and personnel, because in psychological interventions blinding of participants and personnel is not feasible. Also, most studies used self-report measurements and this renders any blinding of the outcome assessors impossible". Andrew: The authors assessed risk of bias via the Cochrane RoB tool, but they reported excluding the criterion for blinding participants/personnel.</t>
+        </is>
+      </c>
+      <c r="FA3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EU3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Yes except they didn't worry about blinding since they say it is not possible in psychological studies. "We decided to exclude the risk-of-bias criterion Blinding of participants and personnel, because in psychological interventions blinding of participants and personnel is not feasible. Also, most studies used self-report measurements and this renders any blinding of the outcome assessors impossible". Andrew: The authors assessed risk of bias via the Cochrane RoB tool, but they reported excluding the criterion for blinding participants/personnel.</t>
-        </is>
-      </c>
-      <c r="EV3" s="1" t="inlineStr">
+      <c r="FB3" s="1" t="inlineStr">
+        <is>
+          <t>Andrew: No information on whether RoB assessment was conducted unilaterally or by multiple reviewers.</t>
+        </is>
+      </c>
+      <c r="FC3" s="1" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="FD3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They mention excluding studies that didn't report what was needed to compute SMDs for meta-analysis. Unsure if they may have been able to get more data to analyze if they had emailed authors. Also did not include the blinding aspect of RoB assessment. Andrew: Unclear concern due to lack of reporting on personnel involved in RoB assessment and exclusion of one RoB tool domain</t>
+        </is>
+      </c>
+      <c r="FE3" s="1" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="FF3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The PRISMA chart suggests they excluded 8 studies with no usable data. It is unclear if these papers did not report data for a reason that could cause bias (e.g., because results were not significant). Also, it is unclear if the authors could have obtained additional data from authors and included these, and regardless, they probably should have been included in the narrative synthesis if not the meta-analysis. Additionally, the PRISMA chart indicates that 38 studies met the inclusion criteria but 27 full-text references were excluded for not reporting original data. It seems unlikely to me that 27/38 full-text references would not have included something useful, like analysis of a follow-up time point. Andrew: Two studies were excluded/unable to be used in meta-analysis due to longer-term (12 and 20 years, same trial) follow-up.</t>
+        </is>
+      </c>
+      <c r="FG3" s="1" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="FH3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: No protocol mentioned. Andrew: No reported protocol</t>
+        </is>
+      </c>
+      <c r="FI3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EW3" s="1" t="inlineStr">
-        <is>
-          <t>Andrew: No information on whether RoB assessment was conducted unilaterally or by multiple reviewers.</t>
-        </is>
-      </c>
-      <c r="EX3" s="1" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="EY3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They mention excluding studies that didn't report what was needed to compute SMDs for meta-analysis. Unsure if they may have been able to get more data to analyze if they had emailed authors. Also did not include the blinding aspect of RoB assessment. Andrew: Unclear concern due to lack of reporting on personnel involved in RoB assessment and exclusion of one RoB tool domain</t>
-        </is>
-      </c>
-      <c r="EZ3" s="1" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="FA3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The PRISMA chart suggests they excluded 8 studies with no usable data. It is unclear if these papers did not report data for a reason that could cause bias (e.g., because results were not significant). Also, it is unclear if the authors could have obtained additional data from authors and included these, and regardless, they probably should have been included in the narrative synthesis if not the meta-analysis. Additionally, the PRISMA chart indicates that 38 studies met the inclusion criteria but 27 full-text references were excluded for not reporting original data. It seems unlikely to me that 27/38 full-text references would not have included something useful, like analysis of a follow-up time point. Andrew: Two studies were excluded/unable to be used in meta-analysis due to longer-term (12 and 20 years, same trial) follow-up.</t>
-        </is>
-      </c>
-      <c r="FB3" s="1" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="FC3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: No protocol mentioned. Andrew: No reported protocol</t>
-        </is>
-      </c>
-      <c r="FD3" s="1" t="inlineStr">
+      <c r="FJ3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They did use a random effects model and use a weighted approach. It is unclear if dependencies should have been/were modeled for effect sizes from different arms of the same studies. It does seem like they most likely grouped the outcomes appropriately (suicidal ideation, suicidal behavior). Andrew: Synthesis was likely appropriate given similarity in study research questions and designs; authors do note high heterogeneity in outcome measures and suggest that included studies may have assessed slightly different constructs</t>
+        </is>
+      </c>
+      <c r="FK3" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FL3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: There was significant heterogeneity and they explored it in the results. Andrew: Random effects model was used to allow for heterogeneity; authors conducted further analyses to examine potential sources of heterogeneity but these did not yield significant findings.</t>
+        </is>
+      </c>
+      <c r="FM3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FE3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They did use a random effects model and use a weighted approach. It is unclear if dependencies should have been/were modeled for effect sizes from different arms of the same studies. It does seem like they most likely grouped the outcomes appropriately (suicidal ideation, suicidal behavior). Andrew: Synthesis was likely appropriate given similarity in study research questions and designs; authors do note high heterogeneity in outcome measures and suggest that included studies may have assessed slightly different constructs</t>
-        </is>
-      </c>
-      <c r="FF3" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FG3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: There was significant heterogeneity and they explored it in the results. Andrew: Random effects model was used to allow for heterogeneity; authors conducted further analyses to examine potential sources of heterogeneity but these did not yield significant findings.</t>
-        </is>
-      </c>
-      <c r="FH3" s="1" t="inlineStr">
+      <c r="FN3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Funnel plots indicate possible publication bias, but they did a fill and trim procedure that indicated it likely did not influence the results too much. Andrew: Authors observed funnel plot asymmetry but trim and fill method did not change the data.</t>
+        </is>
+      </c>
+      <c r="FO3" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FP3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They did not include RoB assessment of blinding, so it is possible the primary studies had high RoB not addressed in the synthesis. They did not really incorporate RoB into the findings. Andrew: Majority of included studies appear to represent low overall risk of bias, but one study with high risk of selection bias and some risk of attrition bias was retained in analyses. Also unclear whether included studies may have been susceptible to blinding/masking-related bias. Potential biases of individual studies were neither accounted for in analyses nor acknowledged in discussion.</t>
+        </is>
+      </c>
+      <c r="FQ3" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="FR3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: No protocol, so uncertain if analyses were pre-planned. RoB assessment was incomplete (did not include blinding). Data modeling strategy was not totally clear (they used a random effects model but it was unclear if they clustered effect sizes within studies when one study had multiple arms). Andrew: Possible risk of bias due to inclusion of one study with multiple potential biases and lack of assessment of blinding/masking-related bias.</t>
+        </is>
+      </c>
+      <c r="FS3" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="FT3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The interpretation did not address several concerns such as inclusion/exclusion criteria (RCTs only, language exclusion, date range, intervention design criteria). Search terms were mostly okay but probably not the best they could have been. No protocol. RoB not fully assessed and not discussed enough in interpretation. Andrew: Interpretation of findings addressed possibilities of publication bias and bias due to language restriction, as well as heterogeneity in outcomes, but not the possibility of individual study biases.</t>
+        </is>
+      </c>
+      <c r="FU3" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FI3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Funnel plots indicate possible publication bias, but they did a fill and trim procedure that indicated it likely did not influence the results too much. Andrew: Authors observed funnel plot asymmetry but trim and fill method did not change the data.</t>
-        </is>
-      </c>
-      <c r="FJ3" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="FK3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They did not include RoB assessment of blinding, so it is possible the primary studies had high RoB not addressed in the synthesis. They did not really incorporate RoB into the findings. Andrew: Majority of included studies appear to represent low overall risk of bias, but one study with high risk of selection bias and some risk of attrition bias was retained in analyses. Also unclear whether included studies may have been susceptible to blinding/masking-related bias. Potential biases of individual studies were neither accounted for in analyses nor acknowledged in discussion.</t>
-        </is>
-      </c>
-      <c r="FL3" s="1" t="inlineStr">
+      <c r="FV3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The analyzed studies seem relevant to the hypothesis, but they may have left out some relevant studies.</t>
+        </is>
+      </c>
+      <c r="FW3" s="1" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="FX3" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They do note that effects are small, and I do not see evidence that they ignored ns effects. They make the claim "In our review, the pooled effect size for SBs was slightly larger than the pooled effect size for SI, indicating that school-based preventive strategies are seemingly more effective in reducing SBs than SI" Not sure if this is appropriate given that different primary studies measured SB and SI, and they did not statistically test whether the two differed.</t>
+        </is>
+      </c>
+      <c r="FY3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="FM3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: No protocol, so uncertain if analyses were pre-planned. RoB assessment was incomplete (did not include blinding). Data modeling strategy was not totally clear (they used a random effects model but it was unclear if they clustered effect sizes within studies when one study had multiple arms). Andrew: Possible risk of bias due to inclusion of one study with multiple potential biases and lack of assessment of blinding/masking-related bias.</t>
-        </is>
-      </c>
-      <c r="FN3" s="1" t="inlineStr">
-        <is>
-          <t>Probably No</t>
-        </is>
-      </c>
-      <c r="FO3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The interpretation did not address several concerns such as inclusion/exclusion criteria (RCTs only, language exclusion, date range, intervention design criteria). Search terms were mostly okay but probably not the best they could have been. No protocol. RoB not fully assessed and not discussed enough in interpretation. Andrew: Interpretation of findings addressed possibilities of publication bias and bias due to language restriction, as well as heterogeneity in outcomes, but not the possibility of individual study biases.</t>
-        </is>
-      </c>
-      <c r="FP3" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FQ3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The analyzed studies seem relevant to the hypothesis, but they may have left out some relevant studies.</t>
-        </is>
-      </c>
-      <c r="FR3" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FS3" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They do note that effects are small, and I do not see evidence that they ignored ns effects. They make the claim "In our review, the pooled effect size for SBs was slightly larger than the pooled effect size for SI, indicating that school-based preventive strategies are seemingly more effective in reducing SBs than SI" Not sure if this is appropriate given that different primary studies measured SB and SI, and they did not statistically test whether the two differed.</t>
-        </is>
-      </c>
-      <c r="FT3" s="1" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="FU3" s="1" t="inlineStr">
+      <c r="FZ3" s="1" t="inlineStr">
         <is>
           <t>Lisa: Several methodological concerns regarding inclusion/exclusion, search, RoB, no attempt to collect data from authors, procedure for title/abstract screening. Analysis technique was not totally clear. The interpretation of findings did seem relatively appropriate, though. Andrew: Unclear concern due primarily to 1) no report of a protocol and 2) no assessment of RoB tool domain for bias related to blinding. Several limitations/potential biases of the review are addressed in the discussion, but not individual study biases.</t>
         </is>
       </c>
     </row>
-    <row r="4" spans="1:177">
+    <row r="4" spans="1:182">
       <c r="A4" s="1">
         <v>12</v>
       </c>
@@ -2482,726 +2564,751 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
+          <t>Open access funding provided by IReL</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="J4" s="1" t="inlineStr">
+      <c r="K4" s="1" t="inlineStr">
         <is>
           <t>PsycINFO, Medline, Education Source, ERIC, Web of Science, Cochrane Central RegisterofControlled Trials</t>
         </is>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>2021_01</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N4" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
           <t>CRD42020168883</t>
         </is>
       </c>
-      <c r="O4" s="1" t="inlineStr">
+      <c r="P4" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="P4" s="1" t="inlineStr">
+      <c r="Q4" s="1" t="inlineStr">
         <is>
           <t>Include: adolescents aged 11–19 years attending post-primary school</t>
         </is>
       </c>
-      <c r="Q4" s="1" t="inlineStr">
+      <c r="R4" s="1" t="inlineStr">
         <is>
           <t>Intervention criteria described in terms of settings (indicated under Settings), not really characteristics of the intervention</t>
         </is>
       </c>
-      <c r="R4" s="1" t="inlineStr">
+      <c r="S4" s="1" t="inlineStr">
         <is>
           <t>Include: contained comparators including no intervention, other intervention, and wait-list control</t>
         </is>
       </c>
-      <c r="S4" s="1" t="inlineStr">
+      <c r="T4" s="1" t="inlineStr">
         <is>
           <t>Include: measuring suicidal thoughts and behaviors (STBs), including suicidal ideation, suicide attempts, planning, and death by suicide.</t>
         </is>
       </c>
-      <c r="T4" s="1" t="inlineStr">
+      <c r="U4" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
+      <c r="V4" s="1" t="inlineStr">
         <is>
           <t>Include: interventions conducted in post-primary school settings</t>
         </is>
       </c>
-      <c r="V4" s="1" t="inlineStr">
+      <c r="W4" s="1" t="inlineStr">
         <is>
           <t>Include: employed CRT study designs. Exclude: non-CRT studies</t>
         </is>
       </c>
-      <c r="W4" s="1" t="inlineStr">
+      <c r="X4" s="1" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
       </c>
-      <c r="X4" s="1" t="inlineStr">
+      <c r="Y4" s="1" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
-      <c r="Y4" s="1" t="inlineStr">
+      <c r="Z4" s="1" t="inlineStr">
         <is>
           <t>School-aged youth</t>
         </is>
       </c>
-      <c r="Z4" s="1" t="inlineStr">
+      <c r="AA4" s="1" t="inlineStr">
         <is>
           <t>School settings</t>
         </is>
       </c>
-      <c r="AA4" s="1" t="inlineStr">
+      <c r="AB4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC4" s="1" t="inlineStr">
+        <is>
+          <t>Cochrane Risk of Bias tool for cluster randomized trials (modified to omit participant blinding and bias in the measurement of the outcome), citation indicates RoB 2.0</t>
+        </is>
+      </c>
+      <c r="AD4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE4" s="1" t="inlineStr">
+        <is>
+          <t>- Excluded blinding of participants and bias in the measurement of the outcome: "The question ‘Were participants aware that they were in a trial?’ and ‘Bias in the measurement of the outcome’ domain were omitted for unsuitability to PSSP research." - Did not do dual assessment for all articles: "Four studies randomly assessed in duplicate by EW and MH demonstrated adequate agreement (j = .63, p = .03)." NOTE THIS DIFFERS FROM PROTOCOL: "Quality will be assessed by at least two reviewers and disagreement regarding bias will be resolved by discussion until consensus is met." - DIFFERENCE FROM PROTOCOL. They did not conduct meta-regression by risk of bias. From PROSPERO: "Sensitivity analysis will be considered to investigate the influence of trials with high risk of bias." - Kappa Value wasn't high (0.63)</t>
+        </is>
+      </c>
+      <c r="AF4" s="1" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="AB4" s="1" t="inlineStr">
+      <c r="AG4" s="1" t="inlineStr">
         <is>
           <t>Intervention</t>
         </is>
       </c>
-      <c r="AC4" s="1" t="inlineStr">
+      <c r="AH4" s="1" t="inlineStr">
         <is>
           <t>Comparator group</t>
         </is>
       </c>
-      <c r="AD4" s="1" t="inlineStr">
+      <c r="AI4" s="1" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="AE4" s="1" t="inlineStr">
+      <c r="AJ4" s="1" t="inlineStr">
         <is>
           <t>Yes, but the description of the intervention was mostly the setting, not details of the intervention.</t>
         </is>
       </c>
-      <c r="AF4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AG4" s="1" t="inlineStr">
+      <c r="AK4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL4" s="1" t="inlineStr">
         <is>
           <t>review questions</t>
         </is>
       </c>
-      <c r="AH4" s="1" t="inlineStr">
+      <c r="AM4" s="1" t="inlineStr">
         <is>
           <t>a search strategy</t>
         </is>
       </c>
-      <c r="AI4" s="1" t="inlineStr">
+      <c r="AN4" s="1" t="inlineStr">
         <is>
           <t>inclusion/exclusion criteria</t>
         </is>
       </c>
-      <c r="AJ4" s="1" t="inlineStr">
+      <c r="AO4" s="1" t="inlineStr">
         <is>
           <t>a risk of bias assessment</t>
         </is>
       </c>
-      <c r="AK4" s="1" t="inlineStr">
+      <c r="AP4" s="1" t="inlineStr">
         <is>
           <t>a meta-analysis/synthesis plan, if appropriate (in the protocol), and</t>
         </is>
       </c>
-      <c r="AL4" s="1" t="inlineStr">
+      <c r="AQ4" s="1" t="inlineStr">
         <is>
           <t>a plan for investigating causes of heterogeneity (in the protocol)</t>
         </is>
       </c>
-      <c r="AM4" s="1" t="inlineStr">
+      <c r="AR4" s="1" t="inlineStr">
         <is>
           <t>justification for any deviations from the protocol (typically reported in the manuscript)</t>
         </is>
       </c>
-      <c r="AN4" s="1" t="inlineStr">
+      <c r="AS4" s="1" t="inlineStr">
         <is>
           <t>Lisa The protocol includes databases to be searched but not search terms. Search terms are provided in the supplementary materials but unclear when they were established. The protocol mentions including risk of bias as a moderator and doing a sensitivity analysis on RoB, but I do not see these analyses specifically reported.  The report does say that no moderators were significant, so it's possible they tested RoB as a moderator and found it ns, but unclear. The protocol says RoB will be coded by two people, but the manuscript indicates only four were double coded. Protocol says they would include individually randomized RCTs but in the paper they only included cluster randomized.  They do explain why it was important to look at cluster randomized, but do not explicitly address the protocol deviation and why they switched away from individually randomized RCTs. Andrew: The authors do not explicitly state that they are working from a protocol. That said, the authors note that their review has been registered with PROSPERO and provide a corresponding registration number. The study protocol is available to the public via the PROSPERO site (ID #CRD42020168883) and includes all requisite AMSTAR components. The authors also include a table in the supplemental material that describes and justifies deviations from the protocol.</t>
         </is>
       </c>
-      <c r="AO4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AP4" s="1" t="inlineStr">
+      <c r="AT4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AU4" s="1" t="inlineStr">
         <is>
           <t>Explanation for including only RCTs</t>
         </is>
       </c>
-      <c r="AR4" s="1" t="inlineStr">
+      <c r="AW4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They explain the need for research on cluster randomized trials e.g., "Rigorous composite effects of PSSP effectiveness on adolescent STBs based on CRTs are needed, consistent with recommendations that randomised and non-randomised studies are generally synthesised separately, particularly when additional sources of heterogeneity associated with CRT designs would likely interact with the intervention, which is the case when schools and classrooms are randomisation units in PSSP research (Borenstein, Hedges, Higgins, &amp; Rothstein, 2011; Donner &amp; Klar, 2002)." Andrew: The review includes only cluster randomized trials (CRTs); the authors explain that rigorous composite effects of prevention programs  targeting adolescents' suicidal thoughts/behaviors are needed, consistent with recommendations that randomized and nonrandomized studies are synthesized separately, particularly when additional sources of heterogeneity associated with CRT designs would likely interact with the intervention, which is the case when schools and classrooms are randomization units. In other words, because intervention conditions are often randomized at the classroom (cluster) level, further analysis of program effects within this design is warranted and allows for analyses of heterogeneity.</t>
         </is>
       </c>
-      <c r="AS4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AT4" s="1" t="inlineStr">
+      <c r="AX4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AY4" s="1" t="inlineStr">
         <is>
           <t>searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU4" s="1" t="inlineStr">
+      <c r="AZ4" s="1" t="inlineStr">
         <is>
           <t>provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AW4" s="1" t="inlineStr">
+      <c r="BB4" s="1" t="inlineStr">
         <is>
           <t>searched the reference lists/bibliographies of included studies</t>
         </is>
       </c>
-      <c r="AX4" s="1" t="inlineStr">
+      <c r="BC4" s="1" t="inlineStr">
         <is>
           <t>searched trial/study registries</t>
         </is>
       </c>
-      <c r="AZ4" s="1" t="inlineStr">
+      <c r="BE4" s="1" t="inlineStr">
         <is>
           <t>conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA4" s="1" t="inlineStr">
+      <c r="BF4" s="1" t="inlineStr">
         <is>
           <t>Lisa: No justification for English restriction or excluding non-peer reviewed studies. Andrew: No justification for restriction to studies published in English. No report of consulting content experts. No search for grey literature given restriction to published studies.</t>
         </is>
       </c>
-      <c r="BB4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BE4" s="1" t="inlineStr">
+      <c r="BG4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BJ4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Titles and abstracts were screened by only one person. Full texts were screened in duplicate. Andrew: Study titles and abstracts were screened for eligibility by only one reviewer. After this reviewer delineated the selection of eligible studies, this sample was screened in duplicate by two reviewers (who subsequently achieved consensus).</t>
         </is>
       </c>
-      <c r="BF4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BH4" s="1" t="inlineStr">
+      <c r="BK4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BM4" s="1" t="inlineStr">
         <is>
           <t>Lisa: It's unclear what was extracted in duplicate but sounds like the most important parts might have  been "EW completed data extraction. EW and CB extracted intervention and contextual factors in duplicate." Unclear if agreement they tested between four studies applies to data extraction or only RoB based on how it was written. Agreement was also not high (only kappa reported not % agreement) "Four studies randomly assessed in duplicate by EW and MH demonstrated adequate agreement (k = .63, p = .03)". Andrew: Data extraction was completed by one reviewer.</t>
         </is>
       </c>
-      <c r="BI4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BJ4" s="1" t="inlineStr">
+      <c r="BN4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO4" s="1" t="inlineStr">
         <is>
           <t>Lisa: PRISMA checklist in the supplement item 16b indicates that this should be on Pages 6 &amp; 9, but I do not see this information anywhere. They do list some exclusion reasons in the text but the numbers of articles described and their reasons do not match the PRISMA chart numbers "Trials were excluded due to the evaluation of non school-based interventions (Poppelaars et al., 2016) and unavailability of crude data (O’Leary-Barrett et al., 2013; Orbach &amp; Hanna, 1993; Randell, Eggert, &amp; Pike, 2001) and for the first follow-up (Vieland, Whittle, Garland, Hicks, &amp; Shaffer, 1991).". Andrew: No list provided (though PRISMA 2020 checklist in supplemental document suggests that this should be on p. 6 &amp; 9 of review)</t>
         </is>
       </c>
-      <c r="BK4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BL4" s="1" t="inlineStr">
+      <c r="BP4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ4" s="1" t="inlineStr">
         <is>
           <t>described populations</t>
         </is>
       </c>
-      <c r="BM4" s="1" t="inlineStr">
+      <c r="BR4" s="1" t="inlineStr">
         <is>
           <t>described interventions</t>
         </is>
       </c>
-      <c r="BN4" s="1" t="inlineStr">
+      <c r="BS4" s="1" t="inlineStr">
         <is>
           <t>described comparators</t>
         </is>
       </c>
-      <c r="BO4" s="1" t="inlineStr">
+      <c r="BT4" s="1" t="inlineStr">
         <is>
           <t>described outcomes</t>
         </is>
       </c>
-      <c r="BP4" s="1" t="inlineStr">
+      <c r="BU4" s="1" t="inlineStr">
         <is>
           <t>described research designs</t>
         </is>
       </c>
-      <c r="BQ4" s="1" t="inlineStr">
+      <c r="BV4" s="1" t="inlineStr">
         <is>
           <t>described population in detail</t>
         </is>
       </c>
-      <c r="BR4" s="1" t="inlineStr">
+      <c r="BW4" s="1" t="inlineStr">
         <is>
           <t>described intervention and comparator in detail (including doses where relevant)</t>
         </is>
       </c>
-      <c r="BS4" s="1" t="inlineStr">
+      <c r="BX4" s="1" t="inlineStr">
         <is>
           <t>described study's setting</t>
         </is>
       </c>
-      <c r="BT4" s="1" t="inlineStr">
+      <c r="BY4" s="1" t="inlineStr">
         <is>
           <t>timeframe for follow-up</t>
         </is>
       </c>
-      <c r="BU4" s="1" t="inlineStr">
+      <c r="BZ4" s="1" t="inlineStr">
         <is>
           <t>Lisa: All studies were cluster randomized, so they did not really need to describe that aspect of the research design. Andrew: All criteria met by Table S3, with the exception of study design (all CRT per eligibility criteria).</t>
         </is>
       </c>
-      <c r="BV4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BY4" s="1" t="inlineStr">
+      <c r="CA4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CD4" s="1" t="inlineStr">
         <is>
           <t>allocation sequence that was not truly random, and</t>
         </is>
       </c>
-      <c r="BZ4" s="1" t="inlineStr">
+      <c r="CE4" s="1" t="inlineStr">
         <is>
           <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
         </is>
       </c>
-      <c r="CA4" s="1" t="inlineStr">
+      <c r="CF4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used RoB 2 but omitted some items. "The question ‘Were participants aware that they were in a trial?’ and ‘Bias in the measurement of the outcome’ domain were omitted for unsuitability to PSSP research." I'm not sure if the "Were participants aware that they were in a trial?" question maps onto unconcealed allocation. Andrew: Reviewers report having used the Cochrane Collaboration RoB Tool for CRTs with the omission of criteria related to blinding and bias in reporting outcome measure, which are appraised as unsuitable to post-primary school-based suicide prevention research. Not sure if the third criterion applies to CRTs.</t>
         </is>
       </c>
-      <c r="CB4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="CG4" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CL4" s="1" t="inlineStr">
+        <is>
           <t>Includes only RCT</t>
         </is>
       </c>
-      <c r="CI4" s="1" t="inlineStr">
+      <c r="CN4" s="1" t="inlineStr">
         <is>
           <t>Includes only RCTs</t>
         </is>
       </c>
-      <c r="CJ4" s="1" t="inlineStr">
+      <c r="CO4" s="1" t="inlineStr">
         <is>
           <t>PRISMA table item 10b indicates that variables for which data are sought are on pages 6-8 of the supplement. I do not see funding information on those pages.</t>
         </is>
       </c>
-      <c r="CK4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CL4" s="1" t="inlineStr">
+      <c r="CP4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CQ4" s="1" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM4" s="1" t="inlineStr">
+      <c r="CR4" s="1" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN4" s="1" t="inlineStr">
+      <c r="CS4" s="1" t="inlineStr">
         <is>
           <t>AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO4" s="1" t="inlineStr">
+      <c r="CT4" s="1" t="inlineStr">
         <is>
           <t>Lisa: I think the analyses themselves are okay but interpreted ns results as if they were significant. Andrew: The authors established the significance/need to obtain rigorous effect sizes for school-based suicide prevention programs using CRT designs; the authors used a random effects model that allowed for heterogeneity and conducted meta-regression in response to high heterogeneity evidenced by forest plot asymmetry and Q/I-squared statistics.</t>
         </is>
       </c>
-      <c r="CP4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CT4" s="1" t="inlineStr">
+      <c r="CU4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY4" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CV4" s="1" t="inlineStr">
+      <c r="DA4" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CX4" s="1" t="inlineStr">
+      <c r="DC4" s="1" t="inlineStr">
         <is>
           <t>Lisa: The protocol says they will do a moderator and sensitivity analysis on RoB but I do not see it in the manuscript. The manuscript does say no moderators were significant, but it is unclear if this includes RoB. Andrew: The authors included 4 CRTs assessed as high risk of bias. The authors suggest that some RoB criteria are irrelevant to review/analysis of CRTs. The authors state that they limited selection bias by synthesizing (pooling?) all available follow-ups and intervention effects, but they did not perform analyses to investigate the possible impact of RoB on summary estimates.</t>
         </is>
       </c>
-      <c r="CY4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DA4" s="1" t="inlineStr">
+      <c r="DD4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DF4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They discuss RoB and a need for different tools but don't really say how it would potentially affect the results. Andrew: The authors included CRTs with variable RoB, but did not discuss how potential biases might have affected either overall estimates or between-study differences.</t>
         </is>
       </c>
-      <c r="DB4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DD4" s="1" t="inlineStr">
+      <c r="DG4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI4" s="1" t="inlineStr">
         <is>
           <t>OR if heterogeneity was present the authors performed an investigation of sources of any heterogeneity in the results and discussed the impact of this on the results of the review</t>
         </is>
       </c>
-      <c r="DE4" s="1" t="inlineStr">
+      <c r="DJ4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They report heterogeneity and do moderator analyses. Andrew: The authors investigated heterogeneity via meta-regression and also discussed how between-study heterogeneity (i.e. multiple effect sizes from the same study vs. effect sizes from other studies) may have influenced results (though they concluded that same-study effects did not unduly influence the overall estimate).</t>
         </is>
       </c>
-      <c r="DF4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DG4" s="1" t="inlineStr">
+      <c r="DK4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DL4" s="1" t="inlineStr">
         <is>
           <t>performed graphical or statistical tests for publication bias and discussed the likelihood and magnitude of impact of publication bias</t>
         </is>
       </c>
-      <c r="DH4" s="1" t="inlineStr">
+      <c r="DM4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Egger's test. Andrew: The authors used Egger's Regression test and determined from non-significant findings that pub. bias was not an issue.</t>
         </is>
       </c>
-      <c r="DI4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DJ4" s="1" t="inlineStr">
+      <c r="DN4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DO4" s="1" t="inlineStr">
         <is>
           <t>The authors reported no competing interests OR</t>
         </is>
       </c>
-      <c r="DM4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DN4" s="1" t="inlineStr">
+      <c r="DR4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DS4" s="1" t="inlineStr">
         <is>
           <t>CRITICALLY LOW</t>
         </is>
       </c>
-      <c r="DO4" s="1" t="inlineStr">
+      <c r="DT4" s="1" t="inlineStr">
         <is>
           <t>Lisa: No on critical items 4 &amp; 7. Andrew: Critical weaknesses in domains 4, 7, possibly 9 (unsure with respect to CRT designs), and 13.</t>
         </is>
       </c>
-      <c r="DP4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DQ4" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Protocol says they would include individually randomized RCTs but in the paper they only included cluster randomized. They do not explain why they deviated on this.</t>
-        </is>
-      </c>
-      <c r="DR4" s="1" t="inlineStr">
+      <c r="DU4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DS4" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Uncertain about why they restricted it only to cluster randomized, as the protocol research objective does not mention that. The paper introduction focuses on the importance of cluster randomized trials, though. I don't want to ding them for this multiple times, though (as a deviation from the protocol under 1.1. and also under 1.4).</t>
-        </is>
-      </c>
-      <c r="DT4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="DV4" s="1" t="inlineStr">
         <is>
+          <t>Lisa: Protocol says they would include individually randomized RCTs but in the paper they only included cluster randomized.  They explain the deviation in Supplement Table S8</t>
+        </is>
+      </c>
+      <c r="DW4" s="1" t="inlineStr">
+        <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DW4" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Uncertain about why they restricted it only to cluster randomized, as the protocol research objective does not mention that. The paper introduction focuses on the importance of cluster randomized trials, though. I don't want to ding them for this multiple times, though (as a deviation from the protocol under 1.1. and also under 1.4).</t>
-        </is>
-      </c>
       <c r="DX4" s="1" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lisa: They  explained why they restricted it only to cluster randomized in Supplement Table S8, as the protocol research objective does not mention that. The paper introduction focuses on the importance of cluster randomized trials also.</t>
         </is>
       </c>
       <c r="DY4" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA4" s="1" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="EB4" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They  explained why they restricted it only to cluster randomized in Supplement Table S8, as the protocol research objective does not mention that. The paper introduction focuses on the importance of cluster randomized trials also.</t>
+        </is>
+      </c>
+      <c r="EC4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="ED4" s="1" t="inlineStr">
+        <is>
           <t>Lisa: Unjustified language restriction. Unjustified restriction to journal articles. Andrew: No justification for restricting eligible studies to peer-reviewed publications available in English, not enough info to determine whether these were appropriate.</t>
         </is>
       </c>
-      <c r="DZ4" s="1" t="inlineStr">
+      <c r="EE4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EA4" s="1" t="inlineStr">
+      <c r="EF4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified language restriction. Unjustified restriction to journal articles. Unclear about change from protocol to manuscript restriction to cluster-randomized. Andrew: High concern given restrictions on language and publication status.</t>
         </is>
       </c>
-      <c r="EB4" s="1" t="inlineStr">
+      <c r="EG4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EC4" s="1" t="inlineStr">
+      <c r="EH4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unclear why they included only published reports, but given that decision the databases seemed appropriate. Andrew: No searches for unpublished reports/grey literature</t>
         </is>
       </c>
-      <c r="ED4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EE4" s="1" t="inlineStr">
+      <c r="EI4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Reference lists. Andrew: Review of included publication reference lists</t>
         </is>
       </c>
-      <c r="EF4" s="1" t="inlineStr">
+      <c r="EK4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EG4" s="1" t="inlineStr">
+      <c r="EL4" s="1" t="inlineStr">
         <is>
           <t>Lisa:  NOT was used to remove reviews. This potentially could have removed reviews with relevant reference lists to look at, but overall okay search for primary studies.</t>
         </is>
       </c>
-      <c r="EH4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="EI4" s="1" t="inlineStr">
+      <c r="EM4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="EN4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified restrictions to English and journal articles. Andrew: No justification for excluding studies not available in English; search strategy excluded unpublished studies.</t>
         </is>
       </c>
-      <c r="EJ4" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="EK4" s="1" t="inlineStr">
+      <c r="EO4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="EP4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Titles and abstracts were single screened but full texts were screened in duplicate. Andrew: Titles and abstracts were screened by only one reviewer (though selection was done in duplicate)</t>
         </is>
       </c>
-      <c r="EL4" s="1" t="inlineStr">
+      <c r="EQ4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EM4" s="1" t="inlineStr">
+      <c r="ER4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified exclusions, single screening of titles and abstracts. Andrew: High concern due to possible publication bias, bias due to language restriction,and bias due to title/abstract screening by one reviewer.</t>
         </is>
       </c>
-      <c r="EN4" s="1" t="inlineStr">
+      <c r="ES4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EO4" s="1" t="inlineStr">
+      <c r="ET4" s="1" t="inlineStr">
         <is>
           <t>Lisa: It's unclear what was extracted in duplicate but sounds like the most important parts might have  been "EW completed data extraction. EW and CB extracted intervention and contextual factors in duplicate." They  mention assessing agreement but it is unclear if this was for data extraction or only RoB. Agreement was also not high (only kappa reported not % agreement) "Four studies randomly assessed in duplicate by EW and MH demonstrated adequate agreement (k = .63, p = .03)". Andrew: Data were extracted by one reviewer.</t>
         </is>
       </c>
-      <c r="EP4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EQ4" s="1" t="inlineStr">
+      <c r="EU4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EV4" s="1" t="inlineStr">
         <is>
           <t>Andrew: Characteristics and effect sizes for each study are reported in Table S3.</t>
         </is>
       </c>
-      <c r="ER4" s="1" t="inlineStr">
+      <c r="EW4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="ES4" s="1" t="inlineStr">
+      <c r="EX4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They contacted authors and transformed things where relevant. It does sound like some were left out due to data unavailability beyond the authors' control. Andrew: Methods section describes strategy for data extraction and, as needed, effect size calculation by reviewers.</t>
         </is>
       </c>
-      <c r="ET4" s="1" t="inlineStr">
+      <c r="EY4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EU4" s="1" t="inlineStr">
+      <c r="EZ4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used RoB 2 but omitted some items. "The question ‘Were participants aware that they were in a trial?’ and ‘Bias in the measurement of the outcome’ domain were omitted for unsuitability to PSSP research."  Andrew: Reviewers reported use of Cochrane Collaborative RoB tool for cluster randomized trials. The authors omitted two RoB tool criteria that they appraised to be unsuitable for school-based suicide prevention research; the authors suggested that omission of these criteria (participant blinding and bias in outcome measurement) is standard practice.</t>
         </is>
       </c>
-      <c r="EV4" s="1" t="inlineStr">
+      <c r="FA4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EW4" s="1" t="inlineStr">
+      <c r="FB4" s="1" t="inlineStr">
         <is>
           <t>Lisa: The protocol says RoB will be coded by two people, but the manuscript indicates only four were double coded. The kappa was .63 which is not high. Andrew: Four studies randomly assessed for RoB in duplicate demonstrated adequate agreement between reviewers</t>
         </is>
       </c>
-      <c r="EX4" s="1" t="inlineStr">
+      <c r="FC4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EY4" s="1" t="inlineStr">
+      <c r="FD4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Insufficient double coding of data and RoB, kappa not high for the four studies that were double coded. Andrew: High concern due to data extraction by one reviewer and RoB assessment in duplicate for only 1/3 of included studies.</t>
         </is>
       </c>
-      <c r="EZ4" s="1" t="inlineStr">
+      <c r="FE4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FA4" s="1" t="inlineStr">
+      <c r="FF4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Data were not able to be located for some studies, so not all were included in the synthesis, although that was not the authors' fault. Between the two forest plots all eligible studies were analyzed. The supplemental table of studies indicates that not all studies included both analyzed outcomes. It has some abbreviations I do not understand but I believe everything was included that they identified. Andrew: Exclusion of one trial that unduly influenced results</t>
         </is>
       </c>
-      <c r="FB4" s="1" t="inlineStr">
+      <c r="FG4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FC4" s="1" t="inlineStr">
+      <c r="FH4" s="1" t="inlineStr">
         <is>
           <t>Lisa: The protocol mentions analyses of individually randomized trials but the paper only included cluster randomized. Although they explain the importance of cluster-randomized. Andrew: Described in Table S8 of supplemental document</t>
         </is>
       </c>
-      <c r="FD4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FF4" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FG4" s="1" t="inlineStr">
+      <c r="FI4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FK4" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FL4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They tested for heterogeneity and tested moderator when needed. Andrew: Between-study heterogeneity was minimal; to the extent that it was observed, meta-regression analyses were conducted.</t>
         </is>
       </c>
-      <c r="FH4" s="1" t="inlineStr">
+      <c r="FM4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FI4" s="1" t="inlineStr">
+      <c r="FN4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They do Egger's test to get at publication bias. Andrew: Outlier study (Shinde et al., 2020) was removed from analyses; results with this study included are presented in Table S5.</t>
         </is>
       </c>
-      <c r="FJ4" s="1" t="inlineStr">
+      <c r="FO4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="FK4" s="1" t="inlineStr">
+      <c r="FP4" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used RoB 2 but omitted some items and still found 4 studies with high concern.They do not analyze RoB like they protocol says they would. Andrew: Four high RoB studies were retained in analyses (notwithstanding that two dimensions of RoB tool were omitted) and no statistical analyses to examine possible effects of high RoB studies on overall estimate.</t>
         </is>
       </c>
-      <c r="FL4" s="1" t="inlineStr">
+      <c r="FQ4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="FM4" s="1" t="inlineStr">
+      <c r="FR4" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unclear how much RoB influenced the results since they did not do a sensitivity analysis or other analysis of RoB. Andrew: Retention of high RoB studies, no analyses of their potential influence.</t>
         </is>
       </c>
-      <c r="FN4" s="1" t="inlineStr">
+      <c r="FS4" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="FO4" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Did not address concerns with inclusion/exclusion, screening, lacking RoB analysis,protocol deviations, etc. Andrew: Concern re: publication status was discussed. No discussion of potential individual study biases or potential biases due to title/abstract screening, data extraction, and 2/3 of RoB assessment by only one reviewer.</t>
-        </is>
-      </c>
-      <c r="FP4" s="1" t="inlineStr">
+      <c r="FT4" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Did not address concerns with inclusion/exclusion, screening, lacking RoB analysis, etc. Andrew: Concern re: publication status was discussed. No discussion of potential individual study biases or potential biases due to title/abstract screening, data extraction, and 2/3 of RoB assessment by only one reviewer.</t>
+        </is>
+      </c>
+      <c r="FU4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FQ4" s="1" t="inlineStr">
+      <c r="FV4" s="1" t="inlineStr">
         <is>
           <t>Lisa: The studies they included are relevant. They may have missed important gray literature,non English studies, and individually randomized RCTs.</t>
         </is>
       </c>
-      <c r="FR4" s="1" t="inlineStr">
+      <c r="FW4" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FT4" s="1" t="inlineStr">
+      <c r="FY4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="FU4" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Inadequate safeguards against study selection, data extraction, and RoB errors. Unjustified exclusion criteria and unjustified deviations from the protocol. Andrew: Retention for analyses of four studies assessed as high RoB, no subsequent analysis to assess possible impact of these studies,  significant aspects of study selection/data extraction/RoB assessment carried out by one reviewer rather than in duplicate.</t>
+      <c r="FZ4" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Inadequate safeguards against study selection, data extraction, and RoB errors. Andrew: Retention for analyses of four studies assessed as high RoB, no subsequent analysis to assess possible impact of these studies,  significant aspects of study selection/data extraction/RoB assessment carried out by one reviewer rather than in duplicate.</t>
         </is>
       </c>
     </row>
-    <row r="5" spans="1:177">
+    <row r="5" spans="1:182">
       <c r="A5" s="1">
         <v>20</v>
       </c>
@@ -3242,661 +3349,658 @@
       </c>
       <c r="I5" s="1" t="inlineStr">
         <is>
+          <t>The study was initiated and funded by the Public Health Agency of Sweden.</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>Scopus, PubMed, PsycINFO, ASSIA</t>
         </is>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>2017_05_07</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="M5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N5" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O5" s="1" t="inlineStr">
+        <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="O5" s="1" t="inlineStr">
+      <c r="P5" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="P5" s="1" t="inlineStr">
+      <c r="Q5" s="1" t="inlineStr">
         <is>
           <t>No participant inclusion/exclusion criteria noted in selection criteria section of manuscript, but PRISMA chart does indicate exclusions based on population.</t>
         </is>
       </c>
-      <c r="Q5" s="1" t="inlineStr">
+      <c r="R5" s="1" t="inlineStr">
         <is>
           <t>Include: education interventions. Exclude: studies evaluating promotion, treatment, and maintenance interventions</t>
         </is>
       </c>
-      <c r="R5" s="1" t="inlineStr">
+      <c r="S5" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="S5" s="1" t="inlineStr">
+      <c r="T5" s="1" t="inlineStr">
         <is>
           <t>Include: suicidal behaviour (suicide, attempts and ideation) and intermediate outcomes (knowledge, attitudes and skills)</t>
         </is>
       </c>
-      <c r="T5" s="1" t="inlineStr">
+      <c r="U5" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="U5" s="1" t="inlineStr">
+      <c r="V5" s="1" t="inlineStr">
         <is>
           <t>Exclude: interventions developed for and conducted in the specific context of prisons, in health care or the national defence forces</t>
         </is>
       </c>
-      <c r="V5" s="1" t="inlineStr">
+      <c r="W5" s="1" t="inlineStr">
         <is>
           <t>Include: studies using a randomised controlled trial (RCT) or quasi-experimental design, Exclude: Results section indicates exclusions were made based on high risk of bias. PRISMA chart indicates some excluded due to language and publication type.</t>
         </is>
       </c>
-      <c r="W5" s="1" t="inlineStr">
+      <c r="X5" s="1" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
       </c>
-      <c r="X5" s="1" t="inlineStr">
+      <c r="Y5" s="1" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
       <c r="AB5" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC5" s="1" t="inlineStr">
+        <is>
+          <t>Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU) Checklist</t>
+        </is>
+      </c>
+      <c r="AD5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AE5" s="1" t="inlineStr">
+        <is>
+          <t>- Description of tool: "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomisation, level of blinding and drop-out rate for the assessment of RCT). Studies were rated as having high, moderate or low risk of bias." Note that SBU website indicates they use Cochrane tools, but unclear here, and this checklist contains more items than Cochrane. - We excluded studies rated as having a high risk of bias (n = 12) - Domain-level RoB not reported for individual primary studies - Unclear how coder conflicts were resolved</t>
+        </is>
+      </c>
+      <c r="AG5" s="1" t="inlineStr">
+        <is>
           <t>Intervention</t>
         </is>
       </c>
-      <c r="AD5" s="1" t="inlineStr">
+      <c r="AI5" s="1" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="AE5" s="1" t="inlineStr">
+      <c r="AJ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: Population not narrowed down and no comparator group in the research question or inclusion/exclusion criterion. The PRISMA chart does indicate some exclusions based on population, but unclear given no mention in inclusion/exclusion criteria. Andrew: Intervention (suicide prevention education) and outcomes of interest are specified. No criteria are stipulated re: population and comparator group. Regarding the latter, both RCT and quasi-experimental designs are eligible.</t>
         </is>
       </c>
-      <c r="AF5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN5" s="1" t="inlineStr">
+      <c r="AK5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AS5" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of protocol. Andrew: No mention of protocol, nor provision of review registration number.</t>
         </is>
       </c>
-      <c r="AO5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AR5" s="1" t="inlineStr">
+      <c r="AT5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AW5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They included both but did not explain why. Andrew: No justification given for inclusion of RCTs and quasi-experimental studies.</t>
         </is>
       </c>
-      <c r="AS5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AT5" s="1" t="inlineStr">
+      <c r="AX5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AY5" s="1" t="inlineStr">
         <is>
           <t>searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU5" s="1" t="inlineStr">
+      <c r="AZ5" s="1" t="inlineStr">
         <is>
           <t>provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AZ5" s="1" t="inlineStr">
+      <c r="BE5" s="1" t="inlineStr">
         <is>
           <t>conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA5" s="1" t="inlineStr">
+      <c r="BF5" s="1" t="inlineStr">
         <is>
           <t>Lisa: Did not provide exact keyword/search strategy. They used language like "terms such as." They didn't mention publication restrictions, but did say they searched for English, Swedish, Danish and Norwegian. Then, the PRISMA chart says they excluded something based on "wrong language" so it seems they may have had exclusion criteria not listed in the Method. Andrew: Authors reported searching for all relevant studies published in English, Swedish, Danish, and Norwegian. It appears that these parameters (language, publication status) may have been applied to the search strategy rather than eligibility criteria. The authors do not justify restricting their purview to published studies in these languages, however. No report of any additional methods indicated above, though authors report having conducted "manual searches" (handsearching?).</t>
         </is>
       </c>
-      <c r="BB5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BC5" s="1" t="inlineStr">
+      <c r="BG5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BH5" s="1" t="inlineStr">
         <is>
           <t>at least two reviewers independently agreed on selection of eligible studies and achieved consensus on which studies to include</t>
         </is>
       </c>
-      <c r="BE5" s="1" t="inlineStr">
+      <c r="BJ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They say they screened titles and abstracts in duplicate. They do not explicitly say they screened full texts in duplicate, but they mention that a third reviewer helped with disagreements, so I think they must have screened them in duplicate.</t>
         </is>
       </c>
-      <c r="BF5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BH5" s="1" t="inlineStr">
+      <c r="BK5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BM5" s="1" t="inlineStr">
         <is>
           <t>Andrew: "I.P., U.B. and E.E. extracted data that enabled evaluation of the primary outcomes: suicide attempts and suicide ideation, as well as the intermediate outcomes of knowledge, attitudes and skills (i.e. gatekeeper referrals of suicidal persons)." (p. 400). Not clear whether this was done in duplicate or divided among authors, nor if there was any process for resolving discrepancies (if done in duplicate).</t>
         </is>
       </c>
-      <c r="BI5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BJ5" s="1" t="inlineStr">
+      <c r="BN5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BO5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They provided counts of numbers of articles excluded for each reason, but not a list of references.</t>
         </is>
       </c>
-      <c r="BK5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BL5" s="1" t="inlineStr">
+      <c r="BP5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ5" s="1" t="inlineStr">
         <is>
           <t>described populations</t>
         </is>
       </c>
-      <c r="BM5" s="1" t="inlineStr">
+      <c r="BR5" s="1" t="inlineStr">
         <is>
           <t>described interventions</t>
         </is>
       </c>
-      <c r="BO5" s="1" t="inlineStr">
+      <c r="BT5" s="1" t="inlineStr">
         <is>
           <t>described outcomes</t>
         </is>
       </c>
-      <c r="BP5" s="1" t="inlineStr">
+      <c r="BU5" s="1" t="inlineStr">
         <is>
           <t>described research designs</t>
         </is>
       </c>
-      <c r="BU5" s="1" t="inlineStr">
+      <c r="BZ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They describe the outcome construct (e.g., suicidal ideation) but not the specific measure. They barely described the populations (just university students, pupils in school, etc., no demographics). Andrew: Unclear if comparator conditions entailed no-treatment control, TAU, or alt. intervention. Interventions are described categorically (i.e. gatekeeper training vs. school-based education), as well as in terms of dosage and name (as applicable). Populations are described in terms of relation to youth and n, but other demographic info (age, gender, race) is omitted.</t>
         </is>
       </c>
-      <c r="BV5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BW5" s="1" t="inlineStr">
-        <is>
-          <t>unconcealed allocation, and</t>
-        </is>
-      </c>
-      <c r="BX5" s="1" t="inlineStr">
+      <c r="CA5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CC5" s="1" t="inlineStr">
         <is>
           <t>lack of blinding of patients and assessors when assessing outcomes (unnecessary for objective outcomes such as all cause mortality)</t>
         </is>
       </c>
-      <c r="BY5" s="1" t="inlineStr">
+      <c r="CD5" s="1" t="inlineStr">
         <is>
           <t>allocation sequence that was not truly random, and</t>
         </is>
       </c>
-      <c r="BZ5" s="1" t="inlineStr">
-        <is>
-          <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
-        </is>
-      </c>
-      <c r="CA5" s="1" t="inlineStr">
+      <c r="CF5" s="1" t="inlineStr">
         <is>
           <t>Lisa:  "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomisation, level of blinding and drop-out rate for the assessment of RCT). Studies were rated as having high, moderate or low risk of bias." No citation provided for this checklist, and I am not sure what exactly is on it.  I googled it, and I see a link to RoB 2 and some other checklists from a similar Swedish agency, so it's possible they used RoB 2 but uncertain. They do not mention different tools for RCTs vs NRSI. Andrew: "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomization, level of blinding and drop-out rate for the assessment of RCT)" (p. 400). Searched for SBU checklist and, at this link (https://www.sbu.se/en/tools-to-assess-risk-of-bias/) read that SBU uses RoB2 and ROBINS-I for randomized/non-randomized studies, respectively. Although this review was published 6 years ago, will assume that "standard criteria" includes selection of reported result.</t>
         </is>
       </c>
-      <c r="CB5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CC5" s="1" t="inlineStr">
-        <is>
-          <t>confounding, and</t>
-        </is>
-      </c>
-      <c r="CD5" s="1" t="inlineStr">
-        <is>
-          <t>selection bias</t>
-        </is>
-      </c>
-      <c r="CE5" s="1" t="inlineStr">
-        <is>
-          <t>methods used to ascertain exposures and outcomes, and</t>
-        </is>
-      </c>
-      <c r="CF5" s="1" t="inlineStr">
-        <is>
-          <t>selection of the reported result from among multiple measurements or analyses of a specified outcome</t>
-        </is>
-      </c>
-      <c r="CH5" s="1" t="inlineStr">
+      <c r="CG5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CM5" s="1" t="inlineStr">
         <is>
           <t>Lisa:  "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomisation, level of blinding and drop-out rate for the assessment of RCT). Studies were rated as having high, moderate or low risk of bias." They don't provide a citation for this checklist, and I am not sure what exactly is on it.  I googled it, and I see a link to RoB 2 and some other checklists from a similar Swedish agency, so it's possible they used RoB 2 but uncertain. They do not mention different tools for RCTs vs NRSI. Andrew: See above; assuming SBU RoB checklist for NRSIs used by authors either was ROBINS-I tool or covered similar criteria. Also noting that all studies of school-based programs were RCTs.</t>
         </is>
       </c>
-      <c r="CI5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CK5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CL5" s="1" t="inlineStr">
+      <c r="CN5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CP5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CQ5" s="1" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM5" s="1" t="inlineStr">
+      <c r="CR5" s="1" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN5" s="1" t="inlineStr">
+      <c r="CS5" s="1" t="inlineStr">
         <is>
           <t>AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO5" s="1" t="inlineStr">
+      <c r="CT5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They explained why some outcomes couldn't be combined in meta-analysis, so it's implied that the ones they did combine were appropriate. Heterogeneity was not high. Andrew: The authors justified combining data on suicidal ideation and attempts into meta-analyses on the bases of shared outcomes/time-points, similar interventions (school-based education), and little to no significant between-study heterogeneity. The authors used weighted random effects models to generate estimates.</t>
         </is>
       </c>
-      <c r="CP5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CT5" s="1" t="inlineStr">
+      <c r="CU5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CY5" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CU5" s="1" t="inlineStr">
+      <c r="CZ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: NRSI were not explicitly separated from RCTs and they do not mention adjusting anything. The analyses relevant for us, though, included only RCTs by chance. Andrew: All studies included in meta-analyses for school-based programs are RCTs (Wasserman et al., 2015; Wilcox et al., 2008; Sandler et al., 2016; Schilling et al., 2016; Aseltine &amp; DeMartino, 2007).</t>
         </is>
       </c>
-      <c r="CV5" s="1" t="inlineStr">
+      <c r="DA5" s="1" t="inlineStr">
         <is>
           <t>No NRSIs</t>
         </is>
       </c>
-      <c r="CX5" s="1" t="inlineStr">
+      <c r="DC5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They excluded high RoB studies but did not include only low (they included moderate). All included were moderate so I don't think it would have been possible to analyze the impact of RoB. Andrew: All studies included were assessed as moderate RoB, no analyses conducted to assess impact of RoB within individual studies</t>
         </is>
       </c>
-      <c r="CY5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CZ5" s="1" t="inlineStr">
+      <c r="DD5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DE5" s="1" t="inlineStr">
         <is>
           <t>OR, if RCTs with moderate or high RoB, or NRSI were included the review provided a discussion of the likely impact of RoB on the results</t>
         </is>
       </c>
-      <c r="DA5" s="1" t="inlineStr">
+      <c r="DF5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They used GRADE and mention the quality of evidence.</t>
         </is>
       </c>
-      <c r="DB5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DC5" s="1" t="inlineStr">
+      <c r="DG5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DH5" s="1" t="inlineStr">
         <is>
           <t>There was no significant heterogeneity in the results</t>
         </is>
       </c>
-      <c r="DE5" s="1" t="inlineStr">
+      <c r="DJ5" s="1" t="inlineStr">
         <is>
           <t>Andrew: No significant heterogeneity in results of school-based education programs; authors did not investigate sources of heterogeneity in other results</t>
         </is>
       </c>
-      <c r="DF5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DH5" s="1" t="inlineStr">
+      <c r="DK5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DM5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They mention that their GRADE process addressed publication bias, but they do not report on graphical or statistical tests. "Thereafter, the confidence was judged with respect to five domains: overall risk of bias, inconsistency between studies (i.e. heterogeneity in results), width of the confidence intervals for the estimate (imprecision), indirectness of study results and the risk of publication bias."</t>
         </is>
       </c>
-      <c r="DI5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DL5" s="1" t="inlineStr">
+      <c r="DN5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DQ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: They disclosed their funding source but do not comment on competing interests. Andrew: Authors acknowledged funding by the Public Health Agency of Sweden, did not report competing interests or no competing interests</t>
         </is>
       </c>
-      <c r="DM5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DN5" s="1" t="inlineStr">
+      <c r="DR5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DS5" s="1" t="inlineStr">
         <is>
           <t>CRITICALLY LOW</t>
         </is>
       </c>
-      <c r="DO5" s="1" t="inlineStr">
+      <c r="DT5" s="1" t="inlineStr">
         <is>
           <t>Lisa: Multiple critical weaknesses including no protocol, unclear explanation of specific searches, no justification for excluding individual studies, unclear RoB process. Andrew: Critical weaknesses in domains 2, 4, 7, 13, 15</t>
         </is>
       </c>
-      <c r="DP5" s="1" t="inlineStr">
+      <c r="DU5" s="1" t="inlineStr">
         <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="DQ5" s="1" t="inlineStr">
+      <c r="DV5" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of protocol</t>
         </is>
       </c>
-      <c r="DR5" s="1" t="inlineStr">
+      <c r="DW5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DS5" s="1" t="inlineStr">
+      <c r="DX5" s="1" t="inlineStr">
         <is>
           <t>Lisa: The criteria they mention in the Method seem appropriate, but the PRISMA chart lists some potentially inappropriate exclusion reasons. Andrew: Eligibility criteria are appropriate to review question, with the disclaimer that authors did not seek to evaluate only school-based programs for youth</t>
         </is>
       </c>
-      <c r="DT5" s="1" t="inlineStr">
+      <c r="DY5" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="DU5" s="1" t="inlineStr">
+      <c r="DZ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: The criteria in the Method don't align with the PRISMA chart reasons for exclusion of full texts. Also, no criteria mentioned the population. Andrew: No criteria for study populations or comparators, also unclear if educational interventions must primarily target suicide or if more generalized programs are eligible so long as suicide outcomes are assessed</t>
         </is>
       </c>
-      <c r="DV5" s="1" t="inlineStr">
+      <c r="EA5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DX5" s="1" t="inlineStr">
+      <c r="EC5" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="DY5" s="1" t="inlineStr">
+      <c r="ED5" s="1" t="inlineStr">
         <is>
           <t>Lisa: As written in the Method they seem appropriate but as written in the PRISMA chart they seem inappropriate without justification (e.g., language and publication type exclusions). Andrew: No eligibility criteria are specified re: sources of info</t>
         </is>
       </c>
-      <c r="DZ5" s="1" t="inlineStr">
+      <c r="EE5" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EA5" s="1" t="inlineStr">
+      <c r="EF5" s="1" t="inlineStr">
         <is>
           <t>Lisa: PRISMA chart indicates unjustified language and publication type exclusions. Some are unclear. Andrew: No protocol, some eligibility criteria are ambiguous or not reported</t>
         </is>
       </c>
-      <c r="EB5" s="1" t="inlineStr">
+      <c r="EG5" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="EH5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The databases seem appropriate. They did not specifically search for unpublished reports, and it seems they may have excluded them, but the databases could have returned some limited unpublished reports. Andrew: No searches for unpublished reports</t>
+        </is>
+      </c>
+      <c r="EI5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EC5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The databases seem appropriate. They did not specifically search for unpublished reports, and it seems they may have excluded them, but the databases could have returned some limited unpublished reports. Andrew: No searches for unpublished reports</t>
-        </is>
-      </c>
-      <c r="ED5" s="1" t="inlineStr">
+      <c r="EJ5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: No mention in article. Andrew: "Manual searches" performed by authors, presumed to describe handsearching</t>
+        </is>
+      </c>
+      <c r="EK5" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="EL5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They do not provide exact search strategies for each database (i.e., they mention terms "such as")</t>
+        </is>
+      </c>
+      <c r="EM5" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="EN5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They did not mention restrictions exactly but they say they searched for articles in English, Swedish, Danish and Norwegian, which implies they excluded other languages without justification. Andrew: Databases searched restricted parameters of studies for consideration to those published in English, Danish, Swedish, and Norwegian. Unclear whether language restrictions were appropriate, publication status restrictions are likely not appropriate.</t>
+        </is>
+      </c>
+      <c r="EO5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EE5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: No mention in article. Andrew: "Manual searches" performed by authors, presumed to describe handsearching</t>
-        </is>
-      </c>
-      <c r="EF5" s="1" t="inlineStr">
+      <c r="EP5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They say they screened titles and abstracts in duplicate. They do not explicitly say they screened full texts in duplicate, but they mention that a third reviewer helped with disagreements, so I think they must have screened them in duplicate.</t>
+        </is>
+      </c>
+      <c r="EQ5" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="ER5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The search terms are not clear enough in the paper. It sounds like they likely excluded based on language which gives me concern, although they did include four languages, which is more than most. Andrew: High concern due to search process restrictions based on sources of info as well as exclusion of unpublished work.</t>
+        </is>
+      </c>
+      <c r="ES5" s="1" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="ET5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Unclear. They say three people extracted data, but they don't discuss resolving discrepancies, so it's unclear if the three extractors overlapped or not. Andrew: Not clear whether data extraction was divided among authors or performed by multiple authors in duplicate; no mention of consensus process</t>
+        </is>
+      </c>
+      <c r="EU5" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EG5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They do not provide exact search strategies for each database (i.e., they mention terms "such as")</t>
-        </is>
-      </c>
-      <c r="EH5" s="1" t="inlineStr">
+      <c r="EV5" s="1" t="inlineStr">
+        <is>
+          <t>Andrew: Sample sizes, assigned weights, and effect sizes (ORs) are reported for all studies used in one or more meta-analyses, though effect sizes are not reported for studies omitted from meta-analyses (due to significant heterogeneity in outcomes). 
+Did not describe comparators.</t>
+        </is>
+      </c>
+      <c r="EW5" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EI5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They did not mention restrictions exactly but they say they searched for articles in English, Swedish, Danish and Norwegian, which implies they excluded other languages without justification. Andrew: Databases searched restricted parameters of studies for consideration to those published in English, Danish, Swedish, and Norwegian. Unclear whether language restrictions were appropriate, publication status restrictions are likely not appropriate.</t>
-        </is>
-      </c>
-      <c r="EJ5" s="1" t="inlineStr">
+      <c r="EX5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: The PRISMA chart indicates they excluded 19 references because they could not find full texts. They do not indicate whether they contacted authors about these. They also do not specify if/how they contacted authors to get effect sizes for included reports, or whether they transformed data to get odds ratios. Andrew: No information on potential transformation of data not in the required format for conversion to odds ratios; several studies used continuous measures for SI and were excluded from meta-analyses.</t>
+        </is>
+      </c>
+      <c r="EY5" s="1" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="EZ5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Unclear. They say "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomisation, level of blinding and drop-out rate for the assessment of RCT). Studies were rated as having high, moderate or low risk of bias." They don't provide a citation for this checklist, and I am not sure what exactly is on it.  I googled it, and I see a link to RoB 2 and some other checklists from a similar Swedish agency, so it's possible they used RoB 2 but uncertain. They do not mention different tools for RCTs vs NRSI. Andrew: RoB and quality were assessed using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU); SBU site currently prescribes use of ROB2/ROBINS-I tools but not certain this was the case in 2017-19 when this review was conducted/published. Specific domains of RoB assessment were not indicated.</t>
+        </is>
+      </c>
+      <c r="FA5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EK5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They say they screened titles and abstracts in duplicate. They do not explicitly say they screened full texts in duplicate, but they mention that a third reviewer helped with disagreements, so I think they must have screened them in duplicate.</t>
-        </is>
-      </c>
-      <c r="EL5" s="1" t="inlineStr">
+      <c r="FB5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They indicate that multiple reviewers independently assessed RoB but it's unclear how they handled discrepancies. Andrew: Unclear if RoB assessment was performed in duplicate.</t>
+        </is>
+      </c>
+      <c r="FC5" s="1" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="FD5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Unclear processes for error minimization in data collection and RoB. Andrew: Insufficient info on minimizing data collection and RoB assessment, apparent exclusion of some study results not in desired format.</t>
+        </is>
+      </c>
+      <c r="FE5" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="FF5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: It appears that they included the relevant included studies. Andrew: Seven of 15 studies measured suicidal ideation on a suicidal scale and were excluded from meta-analyses (presumably because these could no be converted to ORs). Three studies were excluded from meta-analyses on suicide attempts.</t>
+        </is>
+      </c>
+      <c r="FG5" s="1" t="inlineStr">
+        <is>
+          <t>No Information</t>
+        </is>
+      </c>
+      <c r="FH5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: no mention of protocol</t>
+        </is>
+      </c>
+      <c r="FI5" s="1" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="FK5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FL5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: minimal heterogeneity. Andrew: Between-study heterogeneity was minimal.</t>
+        </is>
+      </c>
+      <c r="FM5" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="FN5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They mention that their GRADE process addressed publication bias, but they do not report on graphical or statistical tests. "Thereafter, the confidence was judged with respect to five domains: overall risk of bias, inconsistency between studies (i.e. heterogeneity in results), width of the confidence intervals for the estimate (imprecision), indirectness of study results and the risk of publication bias." Andrew: No evaluation of publication bias.</t>
+        </is>
+      </c>
+      <c r="FO5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FP5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They excluded high RoB studies but included moderate ones. Since all included studies were moderate, they couldn't really analyze effects of RoB on results, although they do use GRADE assessments to address quality of the results. Andrew: All included studies were assessed as moderate RoB; no follow-up analyses were conducted to examine potential impact of individual study biases,</t>
+        </is>
+      </c>
+      <c r="FQ5" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EM5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The search terms are not clear enough in the paper. It sounds like they likely excluded based on language which gives me concern, although they did include four languages, which is more than most. Andrew: High concern due to search process restrictions based on sources of info as well as exclusion of unpublished work.</t>
-        </is>
-      </c>
-      <c r="EN5" s="1" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="EO5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Unclear. They say three people extracted data, but they don't discuss resolving discrepancies, so it's unclear if the three extractors overlapped or not. Andrew: Not clear whether data extraction was divided among authors or performed by multiple authors in duplicate; no mention of consensus process</t>
-        </is>
-      </c>
-      <c r="EP5" s="1" t="inlineStr">
+      <c r="FR5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Unclear influence of RoB and publication bias. Andrew: Probable exclusion of relevant results, no assessment of pub. bias or effect of individual study biases.</t>
+        </is>
+      </c>
+      <c r="FS5" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FT5" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Did not address lack of a protocol, unclear or unjustified inclusion/exclusion decisions. 
+Interpretation of findings addressed RoB and publication bias via GRADE for at least some outcome time points</t>
+        </is>
+      </c>
+      <c r="FU5" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EQ5" s="1" t="inlineStr">
-        <is>
-          <t>Andrew: Sample sizes, assigned weights, and effect sizes (ORs) are reported for all studies used in one or more meta-analyses, though effect sizes are not reported for studies omitted from meta-analyses (due to significant heterogeneity in outcomes).</t>
-        </is>
-      </c>
-      <c r="ER5" s="1" t="inlineStr">
-        <is>
-          <t>Probably No</t>
-        </is>
-      </c>
-      <c r="ES5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: The PRISMA chart indicates they excluded 19 references because they could not find full texts. They do not indicate whether they contacted authors about these. They also do not specify if/how they contacted authors to get effect sizes for included reports, or whether they transformed data to get odds ratios. Andrew: No information on potential transformation of data not in the required format for conversion to odds ratios; several studies used continuous measures for SI and were excluded from meta-analyses.</t>
-        </is>
-      </c>
-      <c r="ET5" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="EU5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Unclear. They say "The external and internal validity of each study was assessed independently by the reviewers I.P., H.L., E.E. and U.B., using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU). The checklist contains a total of 31 questions that refer to standard criteria (e.g. mode of randomisation, level of blinding and drop-out rate for the assessment of RCT). Studies were rated as having high, moderate or low risk of bias." They don't provide a citation for this checklist, and I am not sure what exactly is on it.  I googled it, and I see a link to RoB 2 and some other checklists from a similar Swedish agency, so it's possible they used RoB 2 but uncertain. They do not mention different tools for RCTs vs NRSI. Andrew: RoB and quality were assessed using a checklist developed by the Swedish Council on Health Technology Assessment and Assessment of Social Services (SBU); SBU site currently prescribes use of ROB2/ROBINS-I tools but not certain this was the case in 2017-19 when this review was conducted/published. Specific domains of RoB assessment were not indicated.</t>
-        </is>
-      </c>
-      <c r="EV5" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="EW5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They indicate that multiple reviewers independently assessed RoB but it's unclear how they handled discrepancies. Andrew: Unclear if RoB assessment was performed in duplicate.</t>
-        </is>
-      </c>
-      <c r="EX5" s="1" t="inlineStr">
-        <is>
-          <t>UNCLEAR</t>
-        </is>
-      </c>
-      <c r="EY5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Unclear processes for error minimization in data collection and RoB. Andrew: Insufficient info on minimizing data collection and RoB assessment, apparent exclusion of some study results not in desired format.</t>
-        </is>
-      </c>
-      <c r="EZ5" s="1" t="inlineStr">
-        <is>
-          <t>Probably No</t>
-        </is>
-      </c>
-      <c r="FA5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: It appears that they included the relevant included studies. Andrew: Seven of 15 studies measured suicidal ideation on a suicidal scale and were excluded from meta-analyses (presumably because these could no be converted to ORs). Three studies were excluded from meta-analyses on suicide attempts.</t>
-        </is>
-      </c>
-      <c r="FB5" s="1" t="inlineStr">
-        <is>
-          <t>No Information</t>
-        </is>
-      </c>
-      <c r="FC5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: no mention of protocol</t>
-        </is>
-      </c>
-      <c r="FD5" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FF5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FG5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: minimal heterogeneity. Andrew: Between-study heterogeneity was minimal.</t>
-        </is>
-      </c>
-      <c r="FH5" s="1" t="inlineStr">
-        <is>
-          <t>Probably No</t>
-        </is>
-      </c>
-      <c r="FI5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They mention that their GRADE process addressed publication bias, but they do not report on graphical or statistical tests. "Thereafter, the confidence was judged with respect to five domains: overall risk of bias, inconsistency between studies (i.e. heterogeneity in results), width of the confidence intervals for the estimate (imprecision), indirectness of study results and the risk of publication bias." Andrew: No evaluation of publication bias.</t>
-        </is>
-      </c>
-      <c r="FJ5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="FK5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They excluded high RoB studies but included moderate ones. Since all included studies were moderate, they couldn't really analyze effects of RoB on results, although they do use GRADE assessments to address quality of the results. Andrew: All included studies were assessed as moderate RoB; no follow-up analyses were conducted to examine potential impact of individual study biases,</t>
-        </is>
-      </c>
-      <c r="FL5" s="1" t="inlineStr">
+      <c r="FW5" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY5" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="FM5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Unclear influence of RoB and publication bias. Andrew: Probable exclusion of relevant results, no assessment of pub. bias or effect of individual study biases.</t>
-        </is>
-      </c>
-      <c r="FN5" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="FO5" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Did not address lack of a protocol, unclear or unjustified inclusion/exclusion decisions. Andrew: Interpretation of findings did not address any of the above concerns.</t>
-        </is>
-      </c>
-      <c r="FP5" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FR5" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FT5" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="FU5" s="1" t="inlineStr">
+      <c r="FZ5" s="1" t="inlineStr">
         <is>
           <t>Lisa: Did not address various concerns, including inclusion/exclusion decisions, lack of a protocol, inability to analyze effects of RoB due to all included studies being rated the same. Some aspects are unclear like the search and what effort was made to find full texts. Andrew: High risk of individual study bias in the aggregate affecting effect sizes, high risk of pub. bias due to inclusion of only published studies, possible risk of bias given lack of clarity on whether data extraction/RoB assessment was performed in duplicate, possible bias due to omission of results not in desired format.</t>
         </is>
       </c>
     </row>
-    <row r="6" spans="1:177">
+    <row r="6" spans="1:182">
       <c r="A6" s="1">
         <v>3485</v>
       </c>
@@ -3937,642 +4041,672 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
+          <t>The current project was not financially funded.</t>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="inlineStr">
         <is>
           <t>Education Research Complete, ERIC, PSYCArticles, PsycINFO, Psychology and BehavioralSciences,first 600 dissertation results on ProQuest</t>
         </is>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="M6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="N6" s="1" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O6" s="1" t="inlineStr">
+        <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="P6" s="1" t="inlineStr">
         <is>
           <t>Supplementary data to this article can be found online at https://doi.org/10.1016/j.childyouth.2020.105826</t>
         </is>
       </c>
-      <c r="P6" s="1" t="inlineStr">
+      <c r="Q6" s="1" t="inlineStr">
         <is>
           <t>Inclusion: targeted youth populations, which included K-12 students or college students</t>
         </is>
       </c>
-      <c r="Q6" s="1" t="inlineStr">
+      <c r="R6" s="1" t="inlineStr">
         <is>
           <t>Inclusion: targeting suicide through prevention/intervention or outcome measure, included a treatment group with a suicide prevention focus.</t>
         </is>
       </c>
-      <c r="R6" s="1" t="inlineStr">
+      <c r="S6" s="1" t="inlineStr">
         <is>
           <t>Inclusion: included a control group</t>
         </is>
       </c>
-      <c r="S6" s="1" t="inlineStr">
+      <c r="T6" s="1" t="inlineStr">
         <is>
           <t>Include: targeting suicide through prevention/intervention or outcome measure, included sufficient treatment and control group data to calculate effect sizes post intervention</t>
         </is>
       </c>
-      <c r="T6" s="1" t="inlineStr">
+      <c r="U6" s="1" t="inlineStr">
         <is>
           <t>-999</t>
         </is>
       </c>
-      <c r="U6" s="1" t="inlineStr">
+      <c r="V6" s="1" t="inlineStr">
         <is>
           <t>Inclusion: school or college setting</t>
         </is>
       </c>
-      <c r="V6" s="1" t="inlineStr">
+      <c r="W6" s="1" t="inlineStr">
         <is>
           <t>Include: RCTs, cluster-randomized trials, and quasi-experimental designs</t>
         </is>
       </c>
-      <c r="W6" s="1" t="inlineStr">
+      <c r="X6" s="1" t="inlineStr">
         <is>
           <t>Suicide</t>
         </is>
       </c>
-      <c r="X6" s="1" t="inlineStr">
+      <c r="Y6" s="1" t="inlineStr">
         <is>
           <t>Prevention</t>
         </is>
       </c>
-      <c r="AA6" s="1" t="inlineStr">
+      <c r="AB6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC6" s="1" t="inlineStr">
+        <is>
+          <t>- Bespoke list of items: "To examine how effects differed by methodological quality,we examined moderators of established baseline equivalency (yes, no), design (randomized-control trial, quasi-experimental study), small sample size as indicated by less than 35 participants in one condition (yes, no), length of follow-up time greater than 1 week (yes, no), fidelity (yes, no), collected follow-up data (yes, no), indication of reliable measure (yes, no), and indication of valid measure (yes, no) to determine how effects differed by study quality as an indication of the impact of methodological features on effect sizes." - Quality-related variables were coded and analyzed as moderators.</t>
+        </is>
+      </c>
+      <c r="AD6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AE6" s="1" t="inlineStr">
+        <is>
+          <t>- Quality assessment is missing some domains that could be important, such as blinding. Not clear how quality questions were selected. - They used quality issues to justify excluding grey literature. - No overall ratings provided. Rather than reporting on overall quality, individual quality variables were analyzed as moderators, so overall quality of primary studies is not thoroughly discussed, although individual question ratings are reported in the supplement for each study. - Moderator analysis only done for helping skill and suicide awareness outcomes (likely because of fewer studies for other outcomes).</t>
+        </is>
+      </c>
+      <c r="AF6" s="1" t="inlineStr">
         <is>
           <t>Population</t>
         </is>
       </c>
-      <c r="AB6" s="1" t="inlineStr">
+      <c r="AG6" s="1" t="inlineStr">
         <is>
           <t>Intervention</t>
         </is>
       </c>
-      <c r="AC6" s="1" t="inlineStr">
+      <c r="AH6" s="1" t="inlineStr">
         <is>
           <t>Comparator group</t>
         </is>
       </c>
-      <c r="AD6" s="1" t="inlineStr">
+      <c r="AI6" s="1" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="AE6" s="1" t="inlineStr">
+      <c r="AJ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: The inclusion criteria "targeting suicide through prevention/intervention or outcome measure. Part of the objective is to look at multiple outcomes "Further, no meta-analysis has included the wider criteria of ages and incorporated both positive and negative outcome measures. The current study aims to fill this gap in the literature by exploring the overall effectiveness of suicide prevention programs for school-aged youth on suicide-related and mental health outcomes...". Andrew: Eligible studies needed to include a control group, though no specific control condition(s) were indicated. Eligible studies "included a treatment group with a suicide prevention focus."</t>
         </is>
       </c>
-      <c r="AF6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AN6" s="1" t="inlineStr">
+      <c r="AK6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AS6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of protocol. Andrew: No report of protocol</t>
         </is>
       </c>
-      <c r="AO6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AQ6" s="1" t="inlineStr">
+      <c r="AT6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AV6" s="1" t="inlineStr">
         <is>
           <t>OR Explanation for including both RCTs and NRSI</t>
         </is>
       </c>
-      <c r="AR6" s="1" t="inlineStr">
+      <c r="AW6" s="1" t="inlineStr">
         <is>
           <t>Lisa: "Given the difficulty of conducting randomized controlled trials with school-based universal prevention studies (National Research Council, 2002), randomized controlled trials, clustered-randomized trials, and quasi-experimental studies were all eligible for inclusion." Andrew: "Given the difficulty of conducting randomized controlled trials with school-based universal prevention studies, randomized controlled trials, clustered-randomized trials, and quasi-experimental studies were all eligible for inclusion" (p. 3).</t>
         </is>
       </c>
-      <c r="AS6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AT6" s="1" t="inlineStr">
+      <c r="AX6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AY6" s="1" t="inlineStr">
         <is>
           <t>searched at least 2 databases (relevant to research question)</t>
         </is>
       </c>
-      <c r="AU6" s="1" t="inlineStr">
+      <c r="AZ6" s="1" t="inlineStr">
         <is>
           <t>provided key word and/or search strategy</t>
         </is>
       </c>
-      <c r="AY6" s="1" t="inlineStr">
+      <c r="BB6" s="1" t="inlineStr">
+        <is>
+          <t>searched the reference lists/bibliographies of included studies</t>
+        </is>
+      </c>
+      <c r="BD6" s="1" t="inlineStr">
         <is>
           <t>where relevant, searched for grey literature</t>
         </is>
       </c>
-      <c r="AZ6" s="1" t="inlineStr">
+      <c r="BE6" s="1" t="inlineStr">
         <is>
           <t>conducted search within 24 months of completion of the review</t>
         </is>
       </c>
-      <c r="BA6" s="1" t="inlineStr">
+      <c r="BF6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They say they did not include grey literature initially, and they justify this by citing a study saying it's lower quality, but then they also say they searched ProQuest for grey literature. Uncertain search date, but the upper limit of dates was 2019 and the articles was submitted in 2020, so should be within 24 months. Unjustified language restriction. Andrew: No justification of English language restriction applied to both eligibility criteria and search.</t>
         </is>
       </c>
-      <c r="BB6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BD6" s="1" t="inlineStr">
+      <c r="BG6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BI6" s="1" t="inlineStr">
         <is>
           <t>OR two reviewers selected a sample of eligible studies and achieved good agreement (at least 80 percent), with the remainder selected by one reviewer</t>
         </is>
       </c>
-      <c r="BE6" s="1" t="inlineStr">
+      <c r="BJ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: "Interobserver agreement (IOA) was also conducted for eligibility and inclusion decisions for 25% of screened articles and resulted in 86% agreement." Andrew: Eligible studies were coded by a team of graduate students. "Inter-observer agreement (IOA) was also conducted [by the lead author] for eligibility and inclusion decisions for 25% of screened articles and resulted in 86% agreement." Not clear how the other 75% were selected, whether multiple graduate students each coded all of these articles independently, etc.</t>
         </is>
       </c>
-      <c r="BF6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BG6" s="1" t="inlineStr">
+      <c r="BK6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BL6" s="1" t="inlineStr">
         <is>
           <t>at least two reviewers achieved consensus on which data to extract from included studies</t>
         </is>
       </c>
-      <c r="BH6" s="1" t="inlineStr">
+      <c r="BM6" s="1" t="inlineStr">
         <is>
           <t>Lisa: The coding team completed coding independently and the first author conducted IOA and reviewed the coding as well as flagged any coding disagreements between authors. A total of 14 articles were coded 
 for interobserver agreement out of the possible 27 which resulted in 52% of total articles. The number of potential codings was divided by the total number of possible codings and multiplied by 100, which resulted 
 in 86% agreement. Disagreements were resolved by discussion among coders and the first author until a consensus was reached. After reviewing coding procedures and reaching consensus as a team, coders then reviewed previously coded articles to check for accuracy in coding. Andrew: Described on p. 5 under heading 2.4.3</t>
         </is>
       </c>
-      <c r="BI6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BJ6" s="1" t="inlineStr">
+      <c r="BN6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BO6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No, just counts for each reason in the PRISMA chart.</t>
         </is>
       </c>
-      <c r="BK6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="BL6" s="1" t="inlineStr">
+      <c r="BP6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BQ6" s="1" t="inlineStr">
         <is>
           <t>described populations</t>
         </is>
       </c>
-      <c r="BM6" s="1" t="inlineStr">
+      <c r="BR6" s="1" t="inlineStr">
         <is>
           <t>described interventions</t>
         </is>
       </c>
-      <c r="BP6" s="1" t="inlineStr">
+      <c r="BU6" s="1" t="inlineStr">
         <is>
           <t>described research designs</t>
         </is>
       </c>
-      <c r="BQ6" s="1" t="inlineStr">
+      <c r="BV6" s="1" t="inlineStr">
         <is>
           <t>described population in detail</t>
         </is>
       </c>
-      <c r="BU6" s="1" t="inlineStr">
+      <c r="BZ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Did not describe comparators, and inclusion criteria just said there needed to be a "control." Unclear if they may have included multiple types of controls.  Research designs described in supplement. They describe coding follow-up time frame but I do not see it reported. Andrew: Populations were described in terms of grade level (or grade level[s] served for school personnel), age, and gender distribution. Interventions were described in terms of name, duration, and nature (e.g. gatekeeper training, curriculum-based). Comparator conditions and research designs were not reported on an individual study basis. Outcomes and timeline(s) for follow-up were not reported.</t>
         </is>
       </c>
-      <c r="BV6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="CA6" s="1" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CF6" s="1" t="inlineStr">
+        <is>
           <t>Lisa: Supplemental Table 3 has a quality assessment but no RoB. Andrew: No report of RoB/study quality assessment</t>
         </is>
       </c>
-      <c r="CB6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CH6" s="1" t="inlineStr">
+      <c r="CG6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CM6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Supplemental Table 3 has a quality assessment but no RoB. Andrew: No report of RoB/study quality assessment</t>
         </is>
       </c>
-      <c r="CI6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CK6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CL6" s="1" t="inlineStr">
+      <c r="CN6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CP6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CQ6" s="1" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CM6" s="1" t="inlineStr">
+      <c r="CR6" s="1" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results and adjusted for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CN6" s="1" t="inlineStr">
+      <c r="CS6" s="1" t="inlineStr">
         <is>
           <t>AND investigated the causes of any heterogeneity</t>
         </is>
       </c>
-      <c r="CO6" s="1" t="inlineStr">
+      <c r="CT6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They explain how they grouped different outcomes into different models, but I don't think they explicitly justify combining the data. Andrew: Justification: "[T]here is a paucity of meta-analyses assessing the impact of school-based suicide prevention programs. Further, no meta-analysis has included the wider criteria of ages and incorporated both positive and negative outcome measures." Authors reported use of a random effects technique and adjusted three outliers &gt;3 sd from the mean. In response to high heterogeneity, authors conducted a priori moderator analyses</t>
         </is>
       </c>
-      <c r="CP6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CQ6" s="1" t="inlineStr">
+      <c r="CU6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CV6" s="1" t="inlineStr">
         <is>
           <t>The authors justified combining the data in a meta-analysis</t>
         </is>
       </c>
-      <c r="CR6" s="1" t="inlineStr">
+      <c r="CW6" s="1" t="inlineStr">
         <is>
           <t>AND they used an appropriate weighted technique to combine study results, adjusting for heterogeneity if present</t>
         </is>
       </c>
-      <c r="CU6" s="1" t="inlineStr">
+      <c r="CZ6" s="1" t="inlineStr">
         <is>
           <t>Andrew: No report of adjustment for confounding or combining raw data, no separate estimates for RCTs and NRSIs</t>
         </is>
       </c>
-      <c r="CV6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="CX6" s="1" t="inlineStr">
+      <c r="DA6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DC6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No RoB assessment, although they did look at a quality rating that doesn't appear to have all relevant RoB domains but probably overlaps some. Andrew: No analysis of individual study RoB</t>
         </is>
       </c>
-      <c r="CY6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DA6" s="1" t="inlineStr">
+      <c r="DD6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DF6" s="1" t="inlineStr">
         <is>
           <t>Andrew: No analysis of individual study RoB</t>
         </is>
       </c>
-      <c r="DB6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="DD6" s="1" t="inlineStr">
+      <c r="DG6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="DI6" s="1" t="inlineStr">
         <is>
           <t>OR if heterogeneity was present the authors performed an investigation of sources of any heterogeneity in the results and discussed the impact of this on the results of the review</t>
         </is>
       </c>
-      <c r="DE6" s="1" t="inlineStr">
+      <c r="DJ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Thet tested for heterogeneity and followed up with sensitivity and moderator analyses. Andrew: The authors performed a priori moderator analyses when high heterogeneity in effect sizes for a given outcome were observed and discussed significant sources of heterogeneity (though significance was nullified after removal of one outlier result).</t>
         </is>
       </c>
-      <c r="DF6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DG6" s="1" t="inlineStr">
+      <c r="DK6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DL6" s="1" t="inlineStr">
         <is>
           <t>performed graphical or statistical tests for publication bias and discussed the likelihood and magnitude of impact of publication bias</t>
         </is>
       </c>
-      <c r="DH6" s="1" t="inlineStr">
+      <c r="DM6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They did test for publication bias but didn't really explain how it might have impacted the results. Andrew: Funnel plot analysis and trim-and-fill method. Authors found that publication bias was likely minimal</t>
         </is>
       </c>
-      <c r="DI6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DJ6" s="1" t="inlineStr">
+      <c r="DN6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DO6" s="1" t="inlineStr">
         <is>
           <t>The authors reported no competing interests OR</t>
         </is>
       </c>
-      <c r="DM6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DN6" s="1" t="inlineStr">
+      <c r="DR6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DS6" s="1" t="inlineStr">
         <is>
           <t>CRITICALLY LOW</t>
         </is>
       </c>
-      <c r="DO6" s="1" t="inlineStr">
+      <c r="DT6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Lacking critical domains item 2, 7, 9, 13, 15. Andrew: Critical weaknesses in domains 2, 4, 7, 9, 11b (NRSIs), and 13.</t>
         </is>
       </c>
-      <c r="DP6" s="1" t="inlineStr">
+      <c r="DU6" s="1" t="inlineStr">
         <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="DQ6" s="1" t="inlineStr">
+      <c r="DV6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No protocol mentioned. Andrew: No report of protocol/pre-defined methods</t>
         </is>
       </c>
-      <c r="DR6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DT6" s="1" t="inlineStr">
+      <c r="DW6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DY6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DU6" s="1" t="inlineStr">
+      <c r="DZ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: More detail could have been added on outcomes and comparison groups, but the way it is written, it seems like they were just very inclusive. The objectives/descriptions of the study make it sound like they specifically focused on suicide prevention, but one of the criteria make it sound like maybe other interventions with suicide outcomes could have been eligible "targeting suicide through prevention/intervention or outcome measure". Andrew: It is likely that all possible comparator/control conditions are eligible; preferably, this would be stated rather than implied. It cannot be deduced from reporting of individual study characteristics, either, because comparator conditions of included studies are not described. Reviewers also state that eligible studies "target suicide through prevention/intervention or outcome measure;" the use of "or" is somewhat confusing, though in the context of the whole review it can be inferred that eligible studies might examine multicomponent interventions targeting concerns including, but not limited to, suicide and subsequently measure outcomes related to suicide.</t>
         </is>
       </c>
-      <c r="DV6" s="1" t="inlineStr">
+      <c r="EA6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="DW6" s="1" t="inlineStr">
+      <c r="EB6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They do not justify the date restriction of after 1980, but it seems possiblearticles before then would not generalize to modern times. Andrew: No information re: restriction of eligibility criteria to studies published 1980 or later.</t>
         </is>
       </c>
-      <c r="DX6" s="1" t="inlineStr">
+      <c r="EC6" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="DY6" s="1" t="inlineStr">
+      <c r="ED6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified language restriction, unclear about grey literature. They explain they initially excluded it, and justify the exclusion, but then say they looked at the first 600 proquest results. Andrew: No justification of English language restriction. Authors give rationale for restriction to published studies but conduct grey literature search nonetheless.</t>
         </is>
       </c>
-      <c r="DZ6" s="1" t="inlineStr">
+      <c r="EE6" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EA6" s="1" t="inlineStr">
+      <c r="EF6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No protocol, unjustified exclusions. Andrew: Unclear level of concern, largely due to no report of protocol. Some concern related to restrictions based on sources of info and date, too.</t>
         </is>
       </c>
-      <c r="EB6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ED6" s="1" t="inlineStr">
+      <c r="EG6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EI6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EE6" s="1" t="inlineStr">
+      <c r="EJ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of experts or handsearching but they did search reference lists and "contacted authors to locate potential unpublished studies". Andrew: Reference checking, contacting authors of included studies</t>
         </is>
       </c>
-      <c r="EF6" s="1" t="inlineStr">
+      <c r="EK6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EG6" s="1" t="inlineStr">
+      <c r="EL6" s="1" t="inlineStr">
         <is>
           <t>Lisa: It seems like they could have included some additional terms such as "child" (versus just adolescent), maybe "program"</t>
         </is>
       </c>
-      <c r="EH6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="EI6" s="1" t="inlineStr">
+      <c r="EM6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="EN6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified language and date restrictions. The date range seems reasonable, but the language restriction could introduce bias. Somewhat unclear description of whether grey literature was included/excluded and at what stage. It sounds like they maybe justified excluding it from the main search then went back and looked at the first 600 proquest results. Andrew: Restrictions based on date (1980 or later), and language were applied to the search process; restriction based on pub. status was applied initially and justified, but possibly redacted given reviewers' search for grey literature and consultation with authors of included studies.</t>
         </is>
       </c>
-      <c r="EJ6" s="1" t="inlineStr">
+      <c r="EO6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="EK6" s="1" t="inlineStr">
+      <c r="EP6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They "coded" articles in duplicate, but as written it's not totally clear if this means only data extraction or also screening. They computed agreement, which was sufficient, but does not sound like everything was double screened "Interobserver agreement (IOA) was also conducted for eligibility and inclusion decisions for 25% of screened articles and resulted in 86% agreement. " Andrew: Not clear how many reviewers screened titles and abstracts but selection decisions were made by a coding team, and a 25% sample of decisions for eligible studies were reviewed for inter-observer agreement by first author.</t>
         </is>
       </c>
-      <c r="EL6" s="1" t="inlineStr">
+      <c r="EQ6" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EM6" s="1" t="inlineStr">
+      <c r="ER6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Unjustified exclusions. Andrew: Concern related to date and language restrictions, some ambiguity re: selection process.</t>
         </is>
       </c>
-      <c r="EN6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EO6" s="1" t="inlineStr">
+      <c r="ES6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="ET6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Sounds like they were double coded. Andrew: Detailed checking by lead author</t>
         </is>
       </c>
-      <c r="EP6" s="1" t="inlineStr">
+      <c r="EU6" s="1" t="inlineStr">
         <is>
           <t>Probably No</t>
         </is>
       </c>
-      <c r="EQ6" s="1" t="inlineStr">
+      <c r="EV6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They describe the population and intervention sufficiently, code the study design, intervention dose. They do not describe the control group or RoB. Andrew: No individual study results reported, also missing research designs and comparator conditions.</t>
         </is>
       </c>
-      <c r="ER6" s="1" t="inlineStr">
+      <c r="EW6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="ES6" s="1" t="inlineStr">
+      <c r="EX6" s="1" t="inlineStr">
         <is>
           <t>Lisa: They explain how they computed effect sizes and contacted authors to get more data. The authors they contacted did not reply though. Andrew: Reviewers describe method for data transformation as follows: "when means and standard deviations were unavailable, the sample sizes for means and standard deviations and the p-value an estimation of effect size was created" (p. 5). It is not clear to this coder how data were transformed or imputed, if needed, but evidently reviewers did have a strategy for doing so. Presumably, the review included only continuous measures, though this is never stated.</t>
         </is>
       </c>
-      <c r="ET6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="EU6" s="1" t="inlineStr">
+      <c r="EY6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="EZ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: Study quality was assessed, and it may have some overlap with RoB, but they don't mention allocation concealment. Andrew: No report of RoB assessment</t>
         </is>
       </c>
-      <c r="EV6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="EX6" s="1" t="inlineStr">
+      <c r="FA6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FC6" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="EY6" s="1" t="inlineStr">
+      <c r="FD6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No RoB, more detail could have been reported about comparison groups and individual study outcomes. Andrew: No report of RoB assessment or individual study characteristics</t>
         </is>
       </c>
-      <c r="EZ6" s="1" t="inlineStr">
+      <c r="FE6" s="1" t="inlineStr">
         <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="FA6" s="1" t="inlineStr">
+      <c r="FF6" s="1" t="inlineStr">
         <is>
           <t>Lisa: There was insufficient data reported for some studies, and the authors were unable to retrieve it by contacting authors. It's unclear if they were not reported for a reason that could contribute to bias. The authors identified and adjusted outliers, and I'm not sure if this appropriate, but it does not seem the inappropriately excluded any studies. Table 1 shows three Wasserman intervention arms  and two Petrova intervention arms but there is only 1 Wasserman row and 1 Petrova row in the forest plots. Unclear how they handled studies with multiple arms. Otherwise, all studies in Table 1 are in a forest plot.</t>
         </is>
       </c>
-      <c r="FB6" s="1" t="inlineStr">
+      <c r="FG6" s="1" t="inlineStr">
         <is>
           <t>No Information</t>
         </is>
       </c>
-      <c r="FC6" s="1" t="inlineStr">
+      <c r="FH6" s="1" t="inlineStr">
         <is>
           <t>Lisa: No mention of protocol</t>
         </is>
       </c>
-      <c r="FD6" s="1" t="inlineStr">
+      <c r="FI6" s="1" t="inlineStr">
+        <is>
+          <t>Probably No</t>
+        </is>
+      </c>
+      <c r="FJ6" s="1" t="inlineStr">
+        <is>
+          <t>Andrew: Synthesis was probably appropriate given the similarity in research questions, but RCT and NRSI results are pooled/separate estimates are not reported, and reviewers also created composite outcomes (suicide awareness, helping skill, suicide behavior, psychological wellness, and psychological distress) that may have comprised distinct constructs.</t>
+        </is>
+      </c>
+      <c r="FK6" s="1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FL6" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: They tested for heterogeneity and followed up with moderator analyses. Andrew: When heterogeneity was observed, authors conducted moderator analyses (defined a priori). Authors used a random effects model.</t>
+        </is>
+      </c>
+      <c r="FM6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FE6" s="1" t="inlineStr">
-        <is>
-          <t>Andrew: Synthesis was probably appropriate given the similarity in research questions, but RCT and NRSI results are pooled/separate estimates are not reported, and reviewers also created composite outcomes (suicide awareness, helping skill, suicide behavior, psychological wellness, and psychological distress) that may have comprised distinct constructs.</t>
-        </is>
-      </c>
-      <c r="FF6" s="1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="FG6" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: They tested for heterogeneity and followed up with moderator analyses. Andrew: When heterogeneity was observed, authors conducted moderator analyses (defined a priori). Authors used a random effects model.</t>
-        </is>
-      </c>
-      <c r="FH6" s="1" t="inlineStr">
+      <c r="FN6" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Some funnel plots were symmetrical, but some were asymmetrical. They mention fill and trim but don't really explain if they think the results were robust or how publication bias might have influenced the results.</t>
+        </is>
+      </c>
+      <c r="FO6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FP6" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Not evaluated. Andrew: No info on RoB bias</t>
+        </is>
+      </c>
+      <c r="FQ6" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="FR6" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: No RoB assessment, no protocol to determine if they stuck to pre-planned analysis. Unclear how studies with multiple intervention arms were handled in the analysis. Andrew: High concern due to no reported assessment of individual study RoB</t>
+        </is>
+      </c>
+      <c r="FS6" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="FT6" s="1" t="inlineStr">
+        <is>
+          <t>Lisa: Lack of protocol, RoB, or publication bias discussion not addressed. Description of grey literature inclusion/exclusion lacking. Andrew: No discussion of possible biases of individual studies and implications for results.</t>
+        </is>
+      </c>
+      <c r="FU6" s="1" t="inlineStr">
         <is>
           <t>Probably Yes</t>
         </is>
       </c>
-      <c r="FI6" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Some funnel plots were symmetrical, but some were asymmetrical. They mention fill and trim but don't really explain if they think the results were robust or how publication bias might have influenced the results.</t>
-        </is>
-      </c>
-      <c r="FJ6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="FK6" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Not evaluated. Andrew: No info on RoB bias</t>
-        </is>
-      </c>
-      <c r="FL6" s="1" t="inlineStr">
+      <c r="FW6" s="1" t="inlineStr">
+        <is>
+          <t>Probably Yes</t>
+        </is>
+      </c>
+      <c r="FY6" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="FM6" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: No RoB assessment, no protocol to determine if they stuck to pre-planned analysis. Unclear how studies with multiple intervention arms were handled in the analysis. Andrew: High concern due to no reported assessment of individual study RoB</t>
-        </is>
-      </c>
-      <c r="FN6" s="1" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="FO6" s="1" t="inlineStr">
-        <is>
-          <t>Lisa: Lack of protocol, RoB, or publication bias discussion not addressed. Description of grey literature inclusion/exclusion lacking. Andrew: No discussion of possible biases of individual studies and implications for results.</t>
-        </is>
-      </c>
-      <c r="FP6" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FR6" s="1" t="inlineStr">
-        <is>
-          <t>Probably Yes</t>
-        </is>
-      </c>
-      <c r="FT6" s="1" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="FU6" s="1" t="inlineStr">
+      <c r="FZ6" s="1" t="inlineStr">
         <is>
           <t>Lisa: The largest issues were no protocol and no RoB assessment, along with other smaller things that were not clear. Andrew: High concern due to reviewers' non-report of quality/RoB assessment for included studies. Also, no report of a protocol and no justification for eligibility/search restrictions related to date and language.</t>
         </is>
